--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{18512A66-030D-48CC-98E5-F6DE9E17B26B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -222,6 +222,18 @@
   <si>
     <t>Todays we do volleyball practices.</t>
   </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
 </sst>
 </file>
 
@@ -408,9 +420,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -426,6 +435,9 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -910,74 +922,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="25">
         <v>12622743</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="25"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
     </row>
     <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1070,223 +1082,311 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
+      <c r="A7" s="18">
         <v>46224</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="19">
         <v>480</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <v>50</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="19">
         <v>180</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="19">
         <v>70</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="19">
         <v>200</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="19">
         <v>4</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="19">
         <v>50</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="20">
         <v>1030</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="20">
         <v>100</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="24" t="s">
+      <c r="L7" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
+      <c r="A8" s="18">
         <v>46225</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="19">
         <v>660</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="19">
         <v>180</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="19">
         <v>120</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="19">
         <v>50</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="19">
         <v>0</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="19">
         <v>180</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="20">
         <v>1190</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="20">
         <v>180</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="N8" s="25" t="s">
+      <c r="N8" s="22" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
+      <c r="A9" s="18">
         <v>46226</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="19">
         <v>660</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="19">
         <v>150</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="19">
         <v>150</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="19">
         <v>0</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="19">
         <v>0</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="19">
         <v>150</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="20">
         <v>1110</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="20">
         <v>70</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="M9" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="N9" s="25" t="s">
+      <c r="N9" s="22" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46227</v>
+      </c>
+      <c r="B10" s="14">
+        <v>500</v>
+      </c>
+      <c r="C10" s="14">
+        <v>150</v>
+      </c>
+      <c r="D10" s="14">
+        <v>40</v>
+      </c>
+      <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>240</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>150</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>330</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46228</v>
+      </c>
+      <c r="B11" s="14">
+        <v>520</v>
+      </c>
+      <c r="C11" s="14">
+        <v>180</v>
+      </c>
+      <c r="D11" s="14">
+        <v>50</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>360</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
+      <c r="H11" s="14">
+        <v>180</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46229</v>
+      </c>
+      <c r="B12" s="14">
+        <v>600</v>
+      </c>
+      <c r="C12" s="14">
+        <v>40</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>50</v>
+      </c>
+      <c r="F12" s="14">
+        <v>360</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7</v>
+      </c>
+      <c r="H12" s="14">
+        <v>50</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46230</v>
+      </c>
+      <c r="B13" s="14">
+        <v>560</v>
+      </c>
+      <c r="C13" s="14">
+        <v>50</v>
+      </c>
+      <c r="D13" s="14">
+        <v>180</v>
+      </c>
+      <c r="E13" s="14">
+        <v>40</v>
+      </c>
+      <c r="F13" s="14">
+        <v>240</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>50</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{18512A66-030D-48CC-98E5-F6DE9E17B26B}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD89C775-2BAB-4917-B7A4-DD61081ACDDD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1390,47 +1390,91 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46231</v>
+      </c>
+      <c r="B14" s="14">
+        <v>500</v>
+      </c>
+      <c r="C14" s="14">
+        <v>50</v>
+      </c>
+      <c r="D14" s="14">
+        <v>150</v>
+      </c>
+      <c r="E14" s="14">
+        <v>20</v>
+      </c>
+      <c r="F14" s="14">
+        <v>240</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>50</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46232</v>
+      </c>
+      <c r="B15" s="14">
+        <v>550</v>
+      </c>
+      <c r="C15" s="14">
+        <v>240</v>
+      </c>
+      <c r="D15" s="14">
+        <v>180</v>
+      </c>
+      <c r="E15" s="14">
+        <v>80</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>90</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD89C775-2BAB-4917-B7A4-DD61081ACDDD}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3779093-65A2-436B-B931-8226224F1A60}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Stressed</t>
   </si>
 </sst>
 </file>
@@ -1478,25 +1481,47 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46233</v>
+      </c>
+      <c r="B16" s="14">
+        <v>450</v>
+      </c>
+      <c r="C16" s="14">
+        <v>180</v>
+      </c>
+      <c r="D16" s="14">
+        <v>420</v>
+      </c>
+      <c r="E16" s="14">
+        <v>55</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>50</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1155</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>285</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3779093-65A2-436B-B931-8226224F1A60}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{286B2DE8-06AD-4D5D-9ABD-92BB8FDD7806}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>Stressed</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1089,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="B7" s="19">
         <v>480</v>
@@ -1130,7 +1133,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
-        <v>46225</v>
+        <v>46256</v>
       </c>
       <c r="B8" s="19">
         <v>660</v>
@@ -1174,7 +1177,7 @@
     </row>
     <row r="9" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
-        <v>46226</v>
+        <v>46257</v>
       </c>
       <c r="B9" s="19">
         <v>660</v>
@@ -1218,7 +1221,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="B10" s="14">
         <v>500</v>
@@ -1262,7 +1265,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
-        <v>46228</v>
+        <v>46259</v>
       </c>
       <c r="B11" s="14">
         <v>520</v>
@@ -1306,7 +1309,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="B12" s="14">
         <v>600</v>
@@ -1350,7 +1353,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="B13" s="14">
         <v>560</v>
@@ -1394,7 +1397,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
-        <v>46231</v>
+        <v>46262</v>
       </c>
       <c r="B14" s="14">
         <v>500</v>
@@ -1438,7 +1441,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="B15" s="14">
         <v>550</v>
@@ -1482,7 +1485,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
-        <v>46233</v>
+        <v>46264</v>
       </c>
       <c r="B16" s="14">
         <v>450</v>
@@ -1525,113 +1528,223 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B17" s="14">
+        <v>500</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>320</v>
+      </c>
+      <c r="E17" s="14">
+        <v>50</v>
+      </c>
+      <c r="F17" s="14">
+        <v>240</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>330</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B18" s="14">
+        <v>550</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>10</v>
+      </c>
+      <c r="F18" s="14">
+        <v>420</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>50</v>
+      </c>
+      <c r="D19" s="14">
+        <v>80</v>
+      </c>
+      <c r="E19" s="14">
+        <v>20</v>
+      </c>
+      <c r="F19" s="14">
+        <v>50</v>
+      </c>
+      <c r="G19" s="14">
+        <v>1</v>
+      </c>
+      <c r="H19" s="14">
+        <v>180</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B20" s="14">
+        <v>560</v>
+      </c>
+      <c r="C20" s="14">
+        <v>100</v>
+      </c>
+      <c r="D20" s="14">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14">
+        <v>50</v>
+      </c>
+      <c r="F20" s="14">
+        <v>240</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B21" s="14">
+        <v>500</v>
+      </c>
+      <c r="C21" s="14">
+        <v>50</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>290</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{286B2DE8-06AD-4D5D-9ABD-92BB8FDD7806}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{20CE7353-827B-473A-BA67-A0446C37EA9F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1748,91 +1748,179 @@
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B22" s="14">
+        <v>500</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>200</v>
+      </c>
+      <c r="E22" s="14">
+        <v>59</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>759</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>681</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B23" s="14">
+        <v>720</v>
+      </c>
+      <c r="C23" s="14">
+        <v>180</v>
+      </c>
+      <c r="D23" s="14">
+        <v>240</v>
+      </c>
+      <c r="E23" s="14">
+        <v>50</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>180</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B24" s="14">
+        <v>600</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>300</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>5</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>535</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B25" s="14">
+        <v>550</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>440</v>
+      </c>
+      <c r="E25" s="14">
+        <v>100</v>
+      </c>
+      <c r="F25" s="14">
+        <v>7</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1097</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>343</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{20CE7353-827B-473A-BA67-A0446C37EA9F}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B056BC2-064C-481A-BFA3-B76020C87E36}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="G24" s="14">
         <v>5</v>
@@ -1862,11 +1862,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>905</v>
+        <v>1200</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>535</v>
+        <v>240</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>63</v>
@@ -1890,13 +1890,13 @@
         <v>0</v>
       </c>
       <c r="D25" s="14">
-        <v>440</v>
+        <v>240</v>
       </c>
       <c r="E25" s="14">
         <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>7</v>
+        <v>420</v>
       </c>
       <c r="G25" s="14">
         <v>7</v>
@@ -1906,11 +1906,11 @@
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>1097</v>
+        <v>1310</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>343</v>
+        <v>130</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>65</v>
@@ -1924,65 +1924,125 @@
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B26" s="14">
+        <v>500</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>200</v>
+      </c>
+      <c r="E26" s="14">
+        <v>130</v>
+      </c>
+      <c r="F26" s="14">
+        <v>420</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B27" s="14">
+        <v>450</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>0</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B28" s="14">
+        <v>750</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>0</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>690</v>
       </c>
       <c r="K28" s="16"/>
       <c r="L28" s="16"/>
@@ -1990,21 +2050,37 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B29" s="14">
+        <v>900</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>0</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>540</v>
       </c>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B056BC2-064C-481A-BFA3-B76020C87E36}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{970CEC83-1C96-4598-A53F-7CF536614CFB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>Fever</t>
   </si>
 </sst>
 </file>
@@ -2009,7 +2012,9 @@
       <c r="M27" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="N27" s="17"/>
+      <c r="N27" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
@@ -2044,10 +2049,18 @@
         <f t="shared" si="1"/>
         <v>690</v>
       </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+      <c r="K28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
@@ -2082,10 +2095,18 @@
         <f t="shared" si="1"/>
         <v>540</v>
       </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+      <c r="K29" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{970CEC83-1C96-4598-A53F-7CF536614CFB}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{A82165E3-6211-4D76-936C-AEBAD5F65794}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Fever</t>
+  </si>
+  <si>
+    <t>fever</t>
   </si>
 </sst>
 </file>
@@ -2109,73 +2112,131 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="A30" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B30" s="14">
+        <v>750</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>0</v>
+      </c>
+      <c r="E30" s="14">
+        <v>0</v>
+      </c>
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="H30" s="14">
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+      <c r="A31" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B31" s="14">
+        <v>600</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>108</v>
+      </c>
+      <c r="E31" s="14">
+        <v>50</v>
+      </c>
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="H31" s="14">
+        <v>0</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>758</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>682</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
+      <c r="A32" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B32" s="14">
+        <v>650</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>150</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
+      <c r="A33" s="13">
+        <v>46281</v>
+      </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{A82165E3-6211-4D76-936C-AEBAD5F65794}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{97E5C454-7F34-4274-875A-43140297B640}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2127,8 +2127,12 @@
       <c r="E30" s="14">
         <v>0</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
       <c r="H30" s="14">
         <v>0</v>
       </c>
@@ -2169,18 +2173,22 @@
       <c r="E31" s="14">
         <v>50</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
+      <c r="F31" s="14">
+        <v>200</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
       <c r="H31" s="14">
         <v>0</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>758</v>
+        <v>958</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>682</v>
+        <v>482</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>63</v>
@@ -2209,18 +2217,22 @@
       <c r="E32" s="14">
         <v>90</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
+      <c r="F32" s="14">
+        <v>420</v>
+      </c>
+      <c r="G32" s="14">
+        <v>7</v>
+      </c>
       <c r="H32" s="14">
         <v>0</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>1310</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>130</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>49</v>
@@ -2237,156 +2249,307 @@
       <c r="A33" s="13">
         <v>46281</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="B33" s="14">
+        <v>600</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>180</v>
+      </c>
+      <c r="E33" s="14">
+        <v>50</v>
+      </c>
+      <c r="F33" s="14">
+        <v>420</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>100</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B34" s="14">
+        <v>650</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>40</v>
+      </c>
+      <c r="F34" s="14">
+        <v>240</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>150</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>240</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B35" s="14">
+        <v>700</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>320</v>
+      </c>
+      <c r="E35" s="14">
+        <v>50</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>50</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>20</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B36" s="14">
+        <v>400</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>200</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>780</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B37" s="14">
+        <v>550</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>140</v>
+      </c>
+      <c r="E37" s="14">
+        <v>50</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>60</v>
+      </c>
+      <c r="I37" s="15">
+        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <v>800</v>
+      </c>
+      <c r="J37" s="15">
+        <v>640</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B38" s="14">
+        <v>600</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>52</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>240</v>
+      </c>
+      <c r="G38" s="14">
+        <v>4</v>
+      </c>
+      <c r="H38" s="14">
+        <v>50</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>942</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>498</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B39" s="14">
+        <v>650</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>50</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120</v>
+      </c>
+      <c r="F39" s="14">
+        <v>420</v>
+      </c>
+      <c r="G39" s="14">
+        <v>7</v>
+      </c>
+      <c r="H39" s="14">
+        <v>30</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -2398,14 +2561,8 @@
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
       <c r="K40" s="16"/>
       <c r="L40" s="16"/>
       <c r="M40" s="16"/>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{97E5C454-7F34-4274-875A-43140297B640}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC71A6D7-2B0D-4B34-8F12-C15D1ECE85CE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2553,41 +2553,91 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+      <c r="A40" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B40" s="14">
+        <v>650</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>96</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>420</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>0</v>
+      </c>
+      <c r="I40" s="15">
+        <f t="shared" si="0"/>
+        <v>1196</v>
+      </c>
+      <c r="J40" s="15">
+        <f t="shared" si="1"/>
+        <v>244</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B41" s="14">
+        <v>700</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>200</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>240</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>60</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>240</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC71A6D7-2B0D-4B34-8F12-C15D1ECE85CE}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEA7FA05-D49D-4176-8EA8-9800A6C4AE31}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -188,9 +188,6 @@
   </si>
   <si>
     <t>Medium</t>
-  </si>
-  <si>
-    <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
@@ -886,7 +883,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -956,7 +953,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -973,7 +970,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -981,7 +978,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" s="25"/>
     </row>
@@ -1047,51 +1044,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>46223</v>
-      </c>
-      <c r="B6" s="9">
-        <v>420</v>
-      </c>
-      <c r="C6" s="9">
-        <v>45</v>
-      </c>
-      <c r="D6" s="9">
-        <v>120</v>
-      </c>
-      <c r="E6" s="9">
-        <v>90</v>
-      </c>
-      <c r="F6" s="9">
-        <v>180</v>
-      </c>
-      <c r="G6" s="9">
-        <v>3</v>
-      </c>
-      <c r="H6" s="9">
-        <v>30</v>
-      </c>
-      <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>885</v>
-      </c>
-      <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>555</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>52</v>
-      </c>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
@@ -1128,13 +1095,13 @@
         <v>49</v>
       </c>
       <c r="L7" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="21" t="s">
-        <v>58</v>
-      </c>
       <c r="N7" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1169,16 +1136,16 @@
         <v>180</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M8" s="21" t="s">
         <v>49</v>
       </c>
       <c r="N8" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1213,16 +1180,16 @@
         <v>70</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L9" s="21" t="s">
         <v>49</v>
       </c>
       <c r="M9" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="22" t="s">
         <v>61</v>
-      </c>
-      <c r="N9" s="22" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1251,21 +1218,21 @@
         <v>150</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I6:I69" si="0">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
         <v>1110</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J6:J69" si="1">IF(I10="","",1440-I10)</f>
         <v>330</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N10" s="17"/>
     </row>
@@ -1303,10 +1270,10 @@
         <v>120</v>
       </c>
       <c r="K11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>63</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>64</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>51</v>
@@ -1347,10 +1314,10 @@
         <v>220</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
@@ -1394,7 +1361,7 @@
         <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>51</v>
@@ -1441,7 +1408,7 @@
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N14" s="17"/>
     </row>
@@ -1479,13 +1446,13 @@
         <v>300</v>
       </c>
       <c r="K15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L15" s="16" t="s">
-        <v>64</v>
-      </c>
       <c r="M15" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1523,13 +1490,13 @@
         <v>285</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N16" s="17"/>
     </row>
@@ -1570,7 +1537,7 @@
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>51</v>
@@ -1614,7 +1581,7 @@
         <v>49</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>51</v>
@@ -1655,13 +1622,13 @@
         <v>640</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N19" s="17"/>
     </row>
@@ -1699,13 +1666,13 @@
         <v>490</v>
       </c>
       <c r="K20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L20" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="M20" s="16" t="s">
         <v>64</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>65</v>
       </c>
       <c r="N20" s="17"/>
     </row>
@@ -1743,13 +1710,13 @@
         <v>290</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21" s="16" t="s">
         <v>64</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>65</v>
       </c>
       <c r="N21" s="17"/>
     </row>
@@ -1790,10 +1757,10 @@
         <v>49</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N22" s="17"/>
     </row>
@@ -1831,13 +1798,13 @@
         <v>70</v>
       </c>
       <c r="K23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L23" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L23" s="16" t="s">
-        <v>66</v>
-      </c>
       <c r="M23" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N23" s="17"/>
     </row>
@@ -1875,13 +1842,13 @@
         <v>240</v>
       </c>
       <c r="K24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L24" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L24" s="16" t="s">
-        <v>64</v>
-      </c>
       <c r="M24" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N24" s="17"/>
     </row>
@@ -1919,10 +1886,10 @@
         <v>130</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>51</v>
@@ -1966,7 +1933,7 @@
         <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>51</v>
@@ -2007,16 +1974,16 @@
         <v>690</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L27" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2053,16 +2020,16 @@
         <v>690</v>
       </c>
       <c r="K28" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L28" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L28" s="16" t="s">
-        <v>66</v>
-      </c>
       <c r="M28" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2099,16 +2066,16 @@
         <v>540</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="M29" s="16" t="s">
-        <v>65</v>
-      </c>
       <c r="N29" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2145,16 +2112,16 @@
         <v>690</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L30" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M30" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="M30" s="16" t="s">
-        <v>65</v>
-      </c>
       <c r="N30" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2191,10 +2158,10 @@
         <v>482</v>
       </c>
       <c r="K31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L31" s="16" t="s">
         <v>63</v>
-      </c>
-      <c r="L31" s="16" t="s">
-        <v>64</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>51</v>
@@ -2279,13 +2246,13 @@
         <v>90</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N33" s="17"/>
     </row>
@@ -2323,7 +2290,7 @@
         <v>240</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L34" s="16" t="s">
         <v>50</v>
@@ -2370,7 +2337,7 @@
         <v>49</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M35" s="16" t="s">
         <v>51</v>
@@ -2411,13 +2378,13 @@
         <v>780</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N36" s="17"/>
     </row>
@@ -2454,7 +2421,7 @@
         <v>640</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L37" s="16" t="s">
         <v>50</v>
@@ -2542,7 +2509,7 @@
         <v>170</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>50</v>
@@ -2586,13 +2553,13 @@
         <v>244</v>
       </c>
       <c r="K40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L40" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L40" s="16" t="s">
-        <v>64</v>
-      </c>
       <c r="M40" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N40" s="17"/>
     </row>
@@ -2630,13 +2597,13 @@
         <v>240</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N41" s="17"/>
     </row>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEA7FA05-D49D-4176-8EA8-9800A6C4AE31}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F32329-567D-4E21-83DA-96C74DF18733}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,13 +205,7 @@
     <t>Fine</t>
   </si>
   <si>
-    <t>AVG</t>
-  </si>
-  <si>
     <t xml:space="preserve">week </t>
-  </si>
-  <si>
-    <t>week</t>
   </si>
   <si>
     <t>High</t>
@@ -1095,10 +1089,10 @@
         <v>49</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M7" s="21" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N7" s="22" t="s">
         <v>56</v>
@@ -1136,16 +1130,16 @@
         <v>180</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="N8" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1180,16 +1174,16 @@
         <v>70</v>
       </c>
       <c r="K9" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="22" t="s">
         <v>59</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="M9" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" s="22" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1218,21 +1212,21 @@
         <v>150</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
+        <f t="shared" ref="I10:I69" si="0">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
         <v>1110</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" ref="J6:J69" si="1">IF(I10="","",1440-I10)</f>
+        <f t="shared" ref="J10:J69" si="1">IF(I10="","",1440-I10)</f>
         <v>330</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N10" s="17"/>
     </row>
@@ -1270,10 +1264,10 @@
         <v>120</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>51</v>
@@ -1314,10 +1308,10 @@
         <v>220</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
@@ -1361,7 +1355,7 @@
         <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>51</v>
@@ -1408,7 +1402,7 @@
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N14" s="17"/>
     </row>
@@ -1446,13 +1440,13 @@
         <v>300</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1490,13 +1484,13 @@
         <v>285</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N16" s="17"/>
     </row>
@@ -1537,7 +1531,7 @@
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>51</v>
@@ -1581,7 +1575,7 @@
         <v>49</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>51</v>
@@ -1622,13 +1616,13 @@
         <v>640</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N19" s="17"/>
     </row>
@@ -1666,13 +1660,13 @@
         <v>490</v>
       </c>
       <c r="K20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="16" t="s">
         <v>62</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>64</v>
       </c>
       <c r="N20" s="17"/>
     </row>
@@ -1710,13 +1704,13 @@
         <v>290</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N21" s="17"/>
     </row>
@@ -1757,10 +1751,10 @@
         <v>49</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N22" s="17"/>
     </row>
@@ -1798,13 +1792,13 @@
         <v>70</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N23" s="17"/>
     </row>
@@ -1842,13 +1836,13 @@
         <v>240</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N24" s="17"/>
     </row>
@@ -1886,10 +1880,10 @@
         <v>130</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>51</v>
@@ -1933,7 +1927,7 @@
         <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>51</v>
@@ -1974,16 +1968,16 @@
         <v>690</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L27" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2020,16 +2014,16 @@
         <v>690</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2066,16 +2060,16 @@
         <v>540</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2112,16 +2106,16 @@
         <v>690</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2158,10 +2152,10 @@
         <v>482</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>51</v>
@@ -2246,13 +2240,13 @@
         <v>90</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M33" s="16" t="s">
         <v>62</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>64</v>
       </c>
       <c r="N33" s="17"/>
     </row>
@@ -2290,7 +2284,7 @@
         <v>240</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L34" s="16" t="s">
         <v>50</v>
@@ -2337,7 +2331,7 @@
         <v>49</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M35" s="16" t="s">
         <v>51</v>
@@ -2378,13 +2372,13 @@
         <v>780</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N36" s="17"/>
     </row>
@@ -2421,7 +2415,7 @@
         <v>640</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L37" s="16" t="s">
         <v>50</v>
@@ -2509,7 +2503,7 @@
         <v>170</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>50</v>
@@ -2553,13 +2547,13 @@
         <v>244</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N40" s="17"/>
     </row>
@@ -2597,13 +2591,13 @@
         <v>240</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N41" s="17"/>
     </row>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D41B41064DFFF035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F32329-567D-4E21-83DA-96C74DF18733}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A167787A-F9FD-4851-9173-7DAF0781A426}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -720,186 +725,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="23" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -911,7 +916,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -924,7 +929,7 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
@@ -942,7 +947,7 @@
       <c r="M1" s="24"/>
       <c r="N1" s="24"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -959,7 +964,7 @@
       </c>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -976,7 +981,7 @@
       </c>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
@@ -994,7 +999,7 @@
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1038,7 +1043,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1054,7 +1059,7 @@
       <c r="M6" s="11"/>
       <c r="N6" s="12"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="18">
         <v>46255</v>
       </c>
@@ -1098,7 +1103,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="18">
         <v>46256</v>
       </c>
@@ -1142,7 +1147,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="18">
         <v>46257</v>
       </c>
@@ -1186,7 +1191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
         <v>46258</v>
       </c>
@@ -1230,7 +1235,7 @@
       </c>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
         <v>46259</v>
       </c>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="N11" s="17"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
         <v>46260</v>
       </c>
@@ -1318,7 +1323,7 @@
       </c>
       <c r="N12" s="17"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
         <v>46261</v>
       </c>
@@ -1362,7 +1367,7 @@
       </c>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
         <v>46262</v>
       </c>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="N14" s="17"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13">
         <v>46263</v>
       </c>
@@ -1450,7 +1455,7 @@
       </c>
       <c r="N15" s="17"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13">
         <v>46264</v>
       </c>
@@ -1494,7 +1499,7 @@
       </c>
       <c r="N16" s="17"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13">
         <v>46265</v>
       </c>
@@ -1538,7 +1543,7 @@
       </c>
       <c r="N17" s="17"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
         <v>46266</v>
       </c>
@@ -1582,7 +1587,7 @@
       </c>
       <c r="N18" s="17"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">
         <v>46267</v>
       </c>
@@ -1626,7 +1631,7 @@
       </c>
       <c r="N19" s="17"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
         <v>46268</v>
       </c>
@@ -1670,7 +1675,7 @@
       </c>
       <c r="N20" s="17"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
         <v>46269</v>
       </c>
@@ -1714,7 +1719,7 @@
       </c>
       <c r="N21" s="17"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
         <v>46270</v>
       </c>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="N22" s="17"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13">
         <v>46271</v>
       </c>
@@ -1802,7 +1807,7 @@
       </c>
       <c r="N23" s="17"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
         <v>46272</v>
       </c>
@@ -1846,7 +1851,7 @@
       </c>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13">
         <v>46273</v>
       </c>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
         <v>46274</v>
       </c>
@@ -1934,7 +1939,7 @@
       </c>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">
         <v>46275</v>
       </c>
@@ -1980,7 +1985,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
         <v>46276</v>
       </c>
@@ -2026,7 +2031,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
         <v>46277</v>
       </c>
@@ -2072,7 +2077,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
         <v>46278</v>
       </c>
@@ -2118,7 +2123,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
         <v>46279</v>
       </c>
@@ -2162,7 +2167,7 @@
       </c>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
         <v>46280</v>
       </c>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13">
         <v>46281</v>
       </c>
@@ -2250,7 +2255,7 @@
       </c>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13">
         <v>46282</v>
       </c>
@@ -2294,7 +2299,7 @@
       </c>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
         <v>46283</v>
       </c>
@@ -2338,7 +2343,7 @@
       </c>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
         <v>46284</v>
       </c>
@@ -2382,7 +2387,7 @@
       </c>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13">
         <v>46285</v>
       </c>
@@ -2425,7 +2430,7 @@
       </c>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13">
         <v>46286</v>
       </c>
@@ -2469,7 +2474,7 @@
       </c>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13">
         <v>46287</v>
       </c>
@@ -2513,7 +2518,7 @@
       </c>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="13">
         <v>46288</v>
       </c>
@@ -2557,7 +2562,7 @@
       </c>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13">
         <v>46289</v>
       </c>
@@ -2601,95 +2606,183 @@
       </c>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B42" s="14">
+        <v>650</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>200</v>
+      </c>
+      <c r="E42" s="14">
+        <v>40</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>5</v>
+      </c>
+      <c r="H42" s="14">
+        <v>50</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A43" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B43" s="14">
+        <v>800</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>0</v>
+      </c>
+      <c r="E43" s="14">
+        <v>200</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A44" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B44" s="14">
+        <v>750</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>50</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>200</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A45" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B45" s="14">
+        <v>800</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>0</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>400</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
+        <v>240</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2711,7 +2804,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -2733,7 +2826,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2755,7 +2848,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2777,7 +2870,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2799,7 +2892,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2821,7 +2914,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2843,7 +2936,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2865,7 +2958,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2887,7 +2980,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -2909,7 +3002,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2931,7 +3024,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -2953,7 +3046,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2975,7 +3068,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2997,7 +3090,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -3019,7 +3112,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -3041,7 +3134,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -3063,7 +3156,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -3085,7 +3178,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -3107,7 +3200,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -3129,7 +3222,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -3151,7 +3244,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -3173,7 +3266,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -3195,7 +3288,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -3217,7 +3310,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -3239,7 +3332,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -3261,7 +3354,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -3283,7 +3376,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -3305,7 +3398,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3327,7 +3420,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -3349,7 +3442,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -3371,7 +3464,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -3393,7 +3486,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -3415,7 +3508,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="17"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -3437,7 +3530,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="17"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -3459,7 +3552,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="17"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -3481,7 +3574,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="17"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -3503,7 +3596,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="17"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -3525,7 +3618,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="17"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -3547,7 +3640,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="17"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -3569,7 +3662,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="17"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -3591,7 +3684,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -3613,7 +3706,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -3635,7 +3728,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="17"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -3657,7 +3750,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="17"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -3679,7 +3772,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="17"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -3701,7 +3794,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="17"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -3723,7 +3816,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="17"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -3745,7 +3838,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="17"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -3767,7 +3860,7 @@
       <c r="M94" s="16"/>
       <c r="N94" s="17"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -3789,7 +3882,7 @@
       <c r="M95" s="16"/>
       <c r="N95" s="17"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -3811,7 +3904,7 @@
       <c r="M96" s="16"/>
       <c r="N96" s="17"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -3833,7 +3926,7 @@
       <c r="M97" s="16"/>
       <c r="N97" s="17"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -3855,7 +3948,7 @@
       <c r="M98" s="16"/>
       <c r="N98" s="17"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -3877,7 +3970,7 @@
       <c r="M99" s="16"/>
       <c r="N99" s="17"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -3899,7 +3992,7 @@
       <c r="M100" s="16"/>
       <c r="N100" s="17"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -3921,7 +4014,7 @@
       <c r="M101" s="16"/>
       <c r="N101" s="17"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -3943,7 +4036,7 @@
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -3965,7 +4058,7 @@
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -3987,7 +4080,7 @@
       <c r="M104" s="16"/>
       <c r="N104" s="17"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
@@ -4009,7 +4102,7 @@
       <c r="M105" s="16"/>
       <c r="N105" s="17"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
@@ -4031,7 +4124,7 @@
       <c r="M106" s="16"/>
       <c r="N106" s="17"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -4053,7 +4146,7 @@
       <c r="M107" s="16"/>
       <c r="N107" s="17"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -4075,7 +4168,7 @@
       <c r="M108" s="16"/>
       <c r="N108" s="17"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -4097,7 +4190,7 @@
       <c r="M109" s="16"/>
       <c r="N109" s="17"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -4119,7 +4212,7 @@
       <c r="M110" s="16"/>
       <c r="N110" s="17"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -4141,7 +4234,7 @@
       <c r="M111" s="16"/>
       <c r="N111" s="17"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -4163,7 +4256,7 @@
       <c r="M112" s="16"/>
       <c r="N112" s="17"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -4185,7 +4278,7 @@
       <c r="M113" s="16"/>
       <c r="N113" s="17"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
@@ -4207,7 +4300,7 @@
       <c r="M114" s="16"/>
       <c r="N114" s="17"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
@@ -4229,7 +4322,7 @@
       <c r="M115" s="16"/>
       <c r="N115" s="17"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -4251,7 +4344,7 @@
       <c r="M116" s="16"/>
       <c r="N116" s="17"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -4273,7 +4366,7 @@
       <c r="M117" s="16"/>
       <c r="N117" s="17"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -4295,7 +4388,7 @@
       <c r="M118" s="16"/>
       <c r="N118" s="17"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -4317,7 +4410,7 @@
       <c r="M119" s="16"/>
       <c r="N119" s="17"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -4339,7 +4432,7 @@
       <c r="M120" s="16"/>
       <c r="N120" s="17"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -4361,7 +4454,7 @@
       <c r="M121" s="16"/>
       <c r="N121" s="17"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -4383,7 +4476,7 @@
       <c r="M122" s="16"/>
       <c r="N122" s="17"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -4405,7 +4498,7 @@
       <c r="M123" s="16"/>
       <c r="N123" s="17"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -4427,7 +4520,7 @@
       <c r="M124" s="16"/>
       <c r="N124" s="17"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -4449,7 +4542,7 @@
       <c r="M125" s="16"/>
       <c r="N125" s="17"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -4471,7 +4564,7 @@
       <c r="M126" s="16"/>
       <c r="N126" s="17"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -4493,7 +4586,7 @@
       <c r="M127" s="16"/>
       <c r="N127" s="17"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -4515,7 +4608,7 @@
       <c r="M128" s="16"/>
       <c r="N128" s="17"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -4537,7 +4630,7 @@
       <c r="M129" s="16"/>
       <c r="N129" s="17"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -4559,7 +4652,7 @@
       <c r="M130" s="16"/>
       <c r="N130" s="17"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -4581,7 +4674,7 @@
       <c r="M131" s="16"/>
       <c r="N131" s="17"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -4603,7 +4696,7 @@
       <c r="M132" s="16"/>
       <c r="N132" s="17"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -4625,7 +4718,7 @@
       <c r="M133" s="16"/>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -4647,7 +4740,7 @@
       <c r="M134" s="16"/>
       <c r="N134" s="17"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -4669,7 +4762,7 @@
       <c r="M135" s="16"/>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -4691,7 +4784,7 @@
       <c r="M136" s="16"/>
       <c r="N136" s="17"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -4713,7 +4806,7 @@
       <c r="M137" s="16"/>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
@@ -4735,7 +4828,7 @@
       <c r="M138" s="16"/>
       <c r="N138" s="17"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -4757,7 +4850,7 @@
       <c r="M139" s="16"/>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -4779,7 +4872,7 @@
       <c r="M140" s="16"/>
       <c r="N140" s="17"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
@@ -4801,7 +4894,7 @@
       <c r="M141" s="16"/>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
@@ -4823,7 +4916,7 @@
       <c r="M142" s="16"/>
       <c r="N142" s="17"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
@@ -4845,7 +4938,7 @@
       <c r="M143" s="16"/>
       <c r="N143" s="17"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
@@ -4867,7 +4960,7 @@
       <c r="M144" s="16"/>
       <c r="N144" s="17"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -4889,7 +4982,7 @@
       <c r="M145" s="16"/>
       <c r="N145" s="17"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -4911,7 +5004,7 @@
       <c r="M146" s="16"/>
       <c r="N146" s="17"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -4933,7 +5026,7 @@
       <c r="M147" s="16"/>
       <c r="N147" s="17"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -4955,7 +5048,7 @@
       <c r="M148" s="16"/>
       <c r="N148" s="17"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
@@ -4977,7 +5070,7 @@
       <c r="M149" s="16"/>
       <c r="N149" s="17"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -4999,7 +5092,7 @@
       <c r="M150" s="16"/>
       <c r="N150" s="17"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -5021,7 +5114,7 @@
       <c r="M151" s="16"/>
       <c r="N151" s="17"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -5043,7 +5136,7 @@
       <c r="M152" s="16"/>
       <c r="N152" s="17"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -5065,7 +5158,7 @@
       <c r="M153" s="16"/>
       <c r="N153" s="17"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
@@ -5087,7 +5180,7 @@
       <c r="M154" s="16"/>
       <c r="N154" s="17"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
@@ -5109,7 +5202,7 @@
       <c r="M155" s="16"/>
       <c r="N155" s="17"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
@@ -5131,7 +5224,7 @@
       <c r="M156" s="16"/>
       <c r="N156" s="17"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
@@ -5153,7 +5246,7 @@
       <c r="M157" s="16"/>
       <c r="N157" s="17"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -5175,7 +5268,7 @@
       <c r="M158" s="16"/>
       <c r="N158" s="17"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -5197,7 +5290,7 @@
       <c r="M159" s="16"/>
       <c r="N159" s="17"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -5219,7 +5312,7 @@
       <c r="M160" s="16"/>
       <c r="N160" s="17"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -5241,7 +5334,7 @@
       <c r="M161" s="16"/>
       <c r="N161" s="17"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -5263,7 +5356,7 @@
       <c r="M162" s="16"/>
       <c r="N162" s="17"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -5285,7 +5378,7 @@
       <c r="M163" s="16"/>
       <c r="N163" s="17"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -5307,7 +5400,7 @@
       <c r="M164" s="16"/>
       <c r="N164" s="17"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
@@ -5329,7 +5422,7 @@
       <c r="M165" s="16"/>
       <c r="N165" s="17"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
@@ -5351,7 +5444,7 @@
       <c r="M166" s="16"/>
       <c r="N166" s="17"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -5373,7 +5466,7 @@
       <c r="M167" s="16"/>
       <c r="N167" s="17"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
@@ -5395,7 +5488,7 @@
       <c r="M168" s="16"/>
       <c r="N168" s="17"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
@@ -5417,7 +5510,7 @@
       <c r="M169" s="16"/>
       <c r="N169" s="17"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -5439,7 +5532,7 @@
       <c r="M170" s="16"/>
       <c r="N170" s="17"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -5461,7 +5554,7 @@
       <c r="M171" s="16"/>
       <c r="N171" s="17"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -5483,7 +5576,7 @@
       <c r="M172" s="16"/>
       <c r="N172" s="17"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -5505,7 +5598,7 @@
       <c r="M173" s="16"/>
       <c r="N173" s="17"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -5527,7 +5620,7 @@
       <c r="M174" s="16"/>
       <c r="N174" s="17"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -5549,7 +5642,7 @@
       <c r="M175" s="16"/>
       <c r="N175" s="17"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -5571,7 +5664,7 @@
       <c r="M176" s="16"/>
       <c r="N176" s="17"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -5593,7 +5686,7 @@
       <c r="M177" s="16"/>
       <c r="N177" s="17"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -5615,7 +5708,7 @@
       <c r="M178" s="16"/>
       <c r="N178" s="17"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -5637,7 +5730,7 @@
       <c r="M179" s="16"/>
       <c r="N179" s="17"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -5659,7 +5752,7 @@
       <c r="M180" s="16"/>
       <c r="N180" s="17"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -5681,7 +5774,7 @@
       <c r="M181" s="16"/>
       <c r="N181" s="17"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -5703,7 +5796,7 @@
       <c r="M182" s="16"/>
       <c r="N182" s="17"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -5725,7 +5818,7 @@
       <c r="M183" s="16"/>
       <c r="N183" s="17"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -5747,7 +5840,7 @@
       <c r="M184" s="16"/>
       <c r="N184" s="17"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -5769,7 +5862,7 @@
       <c r="M185" s="16"/>
       <c r="N185" s="17"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -5791,7 +5884,7 @@
       <c r="M186" s="16"/>
       <c r="N186" s="17"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -5813,7 +5906,7 @@
       <c r="M187" s="16"/>
       <c r="N187" s="17"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -5835,7 +5928,7 @@
       <c r="M188" s="16"/>
       <c r="N188" s="17"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -5857,7 +5950,7 @@
       <c r="M189" s="16"/>
       <c r="N189" s="17"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -5879,7 +5972,7 @@
       <c r="M190" s="16"/>
       <c r="N190" s="17"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -5901,7 +5994,7 @@
       <c r="M191" s="16"/>
       <c r="N191" s="17"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -5923,7 +6016,7 @@
       <c r="M192" s="16"/>
       <c r="N192" s="17"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -5945,7 +6038,7 @@
       <c r="M193" s="16"/>
       <c r="N193" s="17"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -5967,7 +6060,7 @@
       <c r="M194" s="16"/>
       <c r="N194" s="17"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -5989,7 +6082,7 @@
       <c r="M195" s="16"/>
       <c r="N195" s="17"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -6011,7 +6104,7 @@
       <c r="M196" s="16"/>
       <c r="N196" s="17"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -6033,7 +6126,7 @@
       <c r="M197" s="16"/>
       <c r="N197" s="17"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -6055,7 +6148,7 @@
       <c r="M198" s="16"/>
       <c r="N198" s="17"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -6077,7 +6170,7 @@
       <c r="M199" s="16"/>
       <c r="N199" s="17"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -6099,7 +6192,7 @@
       <c r="M200" s="16"/>
       <c r="N200" s="17"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -6121,7 +6214,7 @@
       <c r="M201" s="16"/>
       <c r="N201" s="17"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -6143,7 +6236,7 @@
       <c r="M202" s="16"/>
       <c r="N202" s="17"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -6165,7 +6258,7 @@
       <c r="M203" s="16"/>
       <c r="N203" s="17"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -6187,7 +6280,7 @@
       <c r="M204" s="16"/>
       <c r="N204" s="17"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -6209,7 +6302,7 @@
       <c r="M205" s="16"/>
       <c r="N205" s="17"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -6231,7 +6324,7 @@
       <c r="M206" s="16"/>
       <c r="N206" s="17"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -6253,7 +6346,7 @@
       <c r="M207" s="16"/>
       <c r="N207" s="17"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -6275,7 +6368,7 @@
       <c r="M208" s="16"/>
       <c r="N208" s="17"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -6297,7 +6390,7 @@
       <c r="M209" s="16"/>
       <c r="N209" s="17"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -6319,7 +6412,7 @@
       <c r="M210" s="16"/>
       <c r="N210" s="17"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -6341,7 +6434,7 @@
       <c r="M211" s="16"/>
       <c r="N211" s="17"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -6363,7 +6456,7 @@
       <c r="M212" s="16"/>
       <c r="N212" s="17"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -6385,7 +6478,7 @@
       <c r="M213" s="16"/>
       <c r="N213" s="17"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -6407,7 +6500,7 @@
       <c r="M214" s="16"/>
       <c r="N214" s="17"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -6429,7 +6522,7 @@
       <c r="M215" s="16"/>
       <c r="N215" s="17"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -6451,7 +6544,7 @@
       <c r="M216" s="16"/>
       <c r="N216" s="17"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -6473,7 +6566,7 @@
       <c r="M217" s="16"/>
       <c r="N217" s="17"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -6495,7 +6588,7 @@
       <c r="M218" s="16"/>
       <c r="N218" s="17"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -6517,7 +6610,7 @@
       <c r="M219" s="16"/>
       <c r="N219" s="17"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -6539,7 +6632,7 @@
       <c r="M220" s="16"/>
       <c r="N220" s="17"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -6561,7 +6654,7 @@
       <c r="M221" s="16"/>
       <c r="N221" s="17"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -6583,7 +6676,7 @@
       <c r="M222" s="16"/>
       <c r="N222" s="17"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -6605,7 +6698,7 @@
       <c r="M223" s="16"/>
       <c r="N223" s="17"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -6627,7 +6720,7 @@
       <c r="M224" s="16"/>
       <c r="N224" s="17"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -6649,7 +6742,7 @@
       <c r="M225" s="16"/>
       <c r="N225" s="17"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -6671,7 +6764,7 @@
       <c r="M226" s="16"/>
       <c r="N226" s="17"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -6693,7 +6786,7 @@
       <c r="M227" s="16"/>
       <c r="N227" s="17"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -6715,7 +6808,7 @@
       <c r="M228" s="16"/>
       <c r="N228" s="17"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -6737,7 +6830,7 @@
       <c r="M229" s="16"/>
       <c r="N229" s="17"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -6759,7 +6852,7 @@
       <c r="M230" s="16"/>
       <c r="N230" s="17"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -6781,7 +6874,7 @@
       <c r="M231" s="16"/>
       <c r="N231" s="17"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -6803,7 +6896,7 @@
       <c r="M232" s="16"/>
       <c r="N232" s="17"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6825,7 +6918,7 @@
       <c r="M233" s="16"/>
       <c r="N233" s="17"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -6847,7 +6940,7 @@
       <c r="M234" s="16"/>
       <c r="N234" s="17"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -6869,7 +6962,7 @@
       <c r="M235" s="16"/>
       <c r="N235" s="17"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -6891,7 +6984,7 @@
       <c r="M236" s="16"/>
       <c r="N236" s="17"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -6913,7 +7006,7 @@
       <c r="M237" s="16"/>
       <c r="N237" s="17"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -6935,7 +7028,7 @@
       <c r="M238" s="16"/>
       <c r="N238" s="17"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -6957,7 +7050,7 @@
       <c r="M239" s="16"/>
       <c r="N239" s="17"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -6979,7 +7072,7 @@
       <c r="M240" s="16"/>
       <c r="N240" s="17"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -7001,7 +7094,7 @@
       <c r="M241" s="16"/>
       <c r="N241" s="17"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -7023,7 +7116,7 @@
       <c r="M242" s="16"/>
       <c r="N242" s="17"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -7045,7 +7138,7 @@
       <c r="M243" s="16"/>
       <c r="N243" s="17"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -7067,7 +7160,7 @@
       <c r="M244" s="16"/>
       <c r="N244" s="17"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -7089,7 +7182,7 @@
       <c r="M245" s="16"/>
       <c r="N245" s="17"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -7111,7 +7204,7 @@
       <c r="M246" s="16"/>
       <c r="N246" s="17"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -7133,7 +7226,7 @@
       <c r="M247" s="16"/>
       <c r="N247" s="17"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -7155,7 +7248,7 @@
       <c r="M248" s="16"/>
       <c r="N248" s="17"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -7177,7 +7270,7 @@
       <c r="M249" s="16"/>
       <c r="N249" s="17"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -7199,7 +7292,7 @@
       <c r="M250" s="16"/>
       <c r="N250" s="17"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -7221,7 +7314,7 @@
       <c r="M251" s="16"/>
       <c r="N251" s="17"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -7243,7 +7336,7 @@
       <c r="M252" s="16"/>
       <c r="N252" s="17"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -7265,7 +7358,7 @@
       <c r="M253" s="16"/>
       <c r="N253" s="17"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -7287,7 +7380,7 @@
       <c r="M254" s="16"/>
       <c r="N254" s="17"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -7309,7 +7402,7 @@
       <c r="M255" s="16"/>
       <c r="N255" s="17"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -7331,7 +7424,7 @@
       <c r="M256" s="16"/>
       <c r="N256" s="17"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -7353,7 +7446,7 @@
       <c r="M257" s="16"/>
       <c r="N257" s="17"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -7375,7 +7468,7 @@
       <c r="M258" s="16"/>
       <c r="N258" s="17"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -7397,7 +7490,7 @@
       <c r="M259" s="16"/>
       <c r="N259" s="17"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -7419,7 +7512,7 @@
       <c r="M260" s="16"/>
       <c r="N260" s="17"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -7441,7 +7534,7 @@
       <c r="M261" s="16"/>
       <c r="N261" s="17"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -7463,7 +7556,7 @@
       <c r="M262" s="16"/>
       <c r="N262" s="17"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -7485,7 +7578,7 @@
       <c r="M263" s="16"/>
       <c r="N263" s="17"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -7507,7 +7600,7 @@
       <c r="M264" s="16"/>
       <c r="N264" s="17"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -7529,7 +7622,7 @@
       <c r="M265" s="16"/>
       <c r="N265" s="17"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -7551,7 +7644,7 @@
       <c r="M266" s="16"/>
       <c r="N266" s="17"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -7573,7 +7666,7 @@
       <c r="M267" s="16"/>
       <c r="N267" s="17"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -7595,7 +7688,7 @@
       <c r="M268" s="16"/>
       <c r="N268" s="17"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -7617,7 +7710,7 @@
       <c r="M269" s="16"/>
       <c r="N269" s="17"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -7639,7 +7732,7 @@
       <c r="M270" s="16"/>
       <c r="N270" s="17"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -7661,7 +7754,7 @@
       <c r="M271" s="16"/>
       <c r="N271" s="17"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -7683,7 +7776,7 @@
       <c r="M272" s="16"/>
       <c r="N272" s="17"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -7705,7 +7798,7 @@
       <c r="M273" s="16"/>
       <c r="N273" s="17"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -7727,7 +7820,7 @@
       <c r="M274" s="16"/>
       <c r="N274" s="17"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -7749,7 +7842,7 @@
       <c r="M275" s="16"/>
       <c r="N275" s="17"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -7771,7 +7864,7 @@
       <c r="M276" s="16"/>
       <c r="N276" s="17"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -7793,7 +7886,7 @@
       <c r="M277" s="16"/>
       <c r="N277" s="17"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -7815,7 +7908,7 @@
       <c r="M278" s="16"/>
       <c r="N278" s="17"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -7837,7 +7930,7 @@
       <c r="M279" s="16"/>
       <c r="N279" s="17"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -7859,7 +7952,7 @@
       <c r="M280" s="16"/>
       <c r="N280" s="17"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -7881,7 +7974,7 @@
       <c r="M281" s="16"/>
       <c r="N281" s="17"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -7903,7 +7996,7 @@
       <c r="M282" s="16"/>
       <c r="N282" s="17"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -7925,7 +8018,7 @@
       <c r="M283" s="16"/>
       <c r="N283" s="17"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -7947,7 +8040,7 @@
       <c r="M284" s="16"/>
       <c r="N284" s="17"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -7969,7 +8062,7 @@
       <c r="M285" s="16"/>
       <c r="N285" s="17"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -7991,7 +8084,7 @@
       <c r="M286" s="16"/>
       <c r="N286" s="17"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -8013,7 +8106,7 @@
       <c r="M287" s="16"/>
       <c r="N287" s="17"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -8035,7 +8128,7 @@
       <c r="M288" s="16"/>
       <c r="N288" s="17"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -8057,7 +8150,7 @@
       <c r="M289" s="16"/>
       <c r="N289" s="17"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -8079,7 +8172,7 @@
       <c r="M290" s="16"/>
       <c r="N290" s="17"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -8101,7 +8194,7 @@
       <c r="M291" s="16"/>
       <c r="N291" s="17"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -8123,7 +8216,7 @@
       <c r="M292" s="16"/>
       <c r="N292" s="17"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -8145,7 +8238,7 @@
       <c r="M293" s="16"/>
       <c r="N293" s="17"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -8167,7 +8260,7 @@
       <c r="M294" s="16"/>
       <c r="N294" s="17"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -8189,7 +8282,7 @@
       <c r="M295" s="16"/>
       <c r="N295" s="17"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -8211,7 +8304,7 @@
       <c r="M296" s="16"/>
       <c r="N296" s="17"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -8233,7 +8326,7 @@
       <c r="M297" s="16"/>
       <c r="N297" s="17"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -8255,7 +8348,7 @@
       <c r="M298" s="16"/>
       <c r="N298" s="17"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -8277,7 +8370,7 @@
       <c r="M299" s="16"/>
       <c r="N299" s="17"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -8299,7 +8392,7 @@
       <c r="M300" s="16"/>
       <c r="N300" s="17"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -8321,7 +8414,7 @@
       <c r="M301" s="16"/>
       <c r="N301" s="17"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -8343,7 +8436,7 @@
       <c r="M302" s="16"/>
       <c r="N302" s="17"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -8365,7 +8458,7 @@
       <c r="M303" s="16"/>
       <c r="N303" s="17"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -8387,7 +8480,7 @@
       <c r="M304" s="16"/>
       <c r="N304" s="17"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -8409,7 +8502,7 @@
       <c r="M305" s="16"/>
       <c r="N305" s="17"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -8431,7 +8524,7 @@
       <c r="M306" s="16"/>
       <c r="N306" s="17"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -8453,7 +8546,7 @@
       <c r="M307" s="16"/>
       <c r="N307" s="17"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -8475,7 +8568,7 @@
       <c r="M308" s="16"/>
       <c r="N308" s="17"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -8497,7 +8590,7 @@
       <c r="M309" s="16"/>
       <c r="N309" s="17"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -8519,7 +8612,7 @@
       <c r="M310" s="16"/>
       <c r="N310" s="17"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -8541,7 +8634,7 @@
       <c r="M311" s="16"/>
       <c r="N311" s="17"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -8563,7 +8656,7 @@
       <c r="M312" s="16"/>
       <c r="N312" s="17"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -8585,7 +8678,7 @@
       <c r="M313" s="16"/>
       <c r="N313" s="17"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -8607,7 +8700,7 @@
       <c r="M314" s="16"/>
       <c r="N314" s="17"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -8629,7 +8722,7 @@
       <c r="M315" s="16"/>
       <c r="N315" s="17"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -8651,7 +8744,7 @@
       <c r="M316" s="16"/>
       <c r="N316" s="17"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -8673,7 +8766,7 @@
       <c r="M317" s="16"/>
       <c r="N317" s="17"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -8695,7 +8788,7 @@
       <c r="M318" s="16"/>
       <c r="N318" s="17"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -8717,7 +8810,7 @@
       <c r="M319" s="16"/>
       <c r="N319" s="17"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -8739,7 +8832,7 @@
       <c r="M320" s="16"/>
       <c r="N320" s="17"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -8761,7 +8854,7 @@
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -8783,7 +8876,7 @@
       <c r="M322" s="16"/>
       <c r="N322" s="17"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -8805,7 +8898,7 @@
       <c r="M323" s="16"/>
       <c r="N323" s="17"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -8827,7 +8920,7 @@
       <c r="M324" s="16"/>
       <c r="N324" s="17"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -8849,7 +8942,7 @@
       <c r="M325" s="16"/>
       <c r="N325" s="17"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -8871,7 +8964,7 @@
       <c r="M326" s="16"/>
       <c r="N326" s="17"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -8893,7 +8986,7 @@
       <c r="M327" s="16"/>
       <c r="N327" s="17"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -8915,7 +9008,7 @@
       <c r="M328" s="16"/>
       <c r="N328" s="17"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -8937,7 +9030,7 @@
       <c r="M329" s="16"/>
       <c r="N329" s="17"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -8959,7 +9052,7 @@
       <c r="M330" s="16"/>
       <c r="N330" s="17"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -8981,7 +9074,7 @@
       <c r="M331" s="16"/>
       <c r="N331" s="17"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -9003,7 +9096,7 @@
       <c r="M332" s="16"/>
       <c r="N332" s="17"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -9025,7 +9118,7 @@
       <c r="M333" s="16"/>
       <c r="N333" s="17"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -9047,7 +9140,7 @@
       <c r="M334" s="16"/>
       <c r="N334" s="17"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -9069,7 +9162,7 @@
       <c r="M335" s="16"/>
       <c r="N335" s="17"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -9091,7 +9184,7 @@
       <c r="M336" s="16"/>
       <c r="N336" s="17"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -9113,7 +9206,7 @@
       <c r="M337" s="16"/>
       <c r="N337" s="17"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -9135,7 +9228,7 @@
       <c r="M338" s="16"/>
       <c r="N338" s="17"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -9157,7 +9250,7 @@
       <c r="M339" s="16"/>
       <c r="N339" s="17"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -9179,7 +9272,7 @@
       <c r="M340" s="16"/>
       <c r="N340" s="17"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -9201,7 +9294,7 @@
       <c r="M341" s="16"/>
       <c r="N341" s="17"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -9223,7 +9316,7 @@
       <c r="M342" s="16"/>
       <c r="N342" s="17"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -9245,7 +9338,7 @@
       <c r="M343" s="16"/>
       <c r="N343" s="17"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -9267,7 +9360,7 @@
       <c r="M344" s="16"/>
       <c r="N344" s="17"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -9289,7 +9382,7 @@
       <c r="M345" s="16"/>
       <c r="N345" s="17"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -9311,7 +9404,7 @@
       <c r="M346" s="16"/>
       <c r="N346" s="17"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -9333,7 +9426,7 @@
       <c r="M347" s="16"/>
       <c r="N347" s="17"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -9355,7 +9448,7 @@
       <c r="M348" s="16"/>
       <c r="N348" s="17"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -9377,7 +9470,7 @@
       <c r="M349" s="16"/>
       <c r="N349" s="17"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -9399,7 +9492,7 @@
       <c r="M350" s="16"/>
       <c r="N350" s="17"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -9421,7 +9514,7 @@
       <c r="M351" s="16"/>
       <c r="N351" s="17"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -9443,7 +9536,7 @@
       <c r="M352" s="16"/>
       <c r="N352" s="17"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -9465,7 +9558,7 @@
       <c r="M353" s="16"/>
       <c r="N353" s="17"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -9487,7 +9580,7 @@
       <c r="M354" s="16"/>
       <c r="N354" s="17"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -9509,7 +9602,7 @@
       <c r="M355" s="16"/>
       <c r="N355" s="17"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -9531,7 +9624,7 @@
       <c r="M356" s="16"/>
       <c r="N356" s="17"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -9553,7 +9646,7 @@
       <c r="M357" s="16"/>
       <c r="N357" s="17"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -9575,7 +9668,7 @@
       <c r="M358" s="16"/>
       <c r="N358" s="17"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -9597,7 +9690,7 @@
       <c r="M359" s="16"/>
       <c r="N359" s="17"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -9619,7 +9712,7 @@
       <c r="M360" s="16"/>
       <c r="N360" s="17"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -9641,7 +9734,7 @@
       <c r="M361" s="16"/>
       <c r="N361" s="17"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -9663,7 +9756,7 @@
       <c r="M362" s="16"/>
       <c r="N362" s="17"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -9685,7 +9778,7 @@
       <c r="M363" s="16"/>
       <c r="N363" s="17"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -9707,7 +9800,7 @@
       <c r="M364" s="16"/>
       <c r="N364" s="17"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -9729,7 +9822,7 @@
       <c r="M365" s="16"/>
       <c r="N365" s="17"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -9751,7 +9844,7 @@
       <c r="M366" s="16"/>
       <c r="N366" s="17"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -9773,7 +9866,7 @@
       <c r="M367" s="16"/>
       <c r="N367" s="17"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -9795,7 +9888,7 @@
       <c r="M368" s="16"/>
       <c r="N368" s="17"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -9817,7 +9910,7 @@
       <c r="M369" s="16"/>
       <c r="N369" s="17"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -9839,7 +9932,7 @@
       <c r="M370" s="16"/>
       <c r="N370" s="17"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -9861,7 +9954,7 @@
       <c r="M371" s="16"/>
       <c r="N371" s="17"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -9883,7 +9976,7 @@
       <c r="M372" s="16"/>
       <c r="N372" s="17"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -9905,7 +9998,7 @@
       <c r="M373" s="16"/>
       <c r="N373" s="17"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -9927,7 +10020,7 @@
       <c r="M374" s="16"/>
       <c r="N374" s="17"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -9949,7 +10042,7 @@
       <c r="M375" s="16"/>
       <c r="N375" s="17"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -9971,7 +10064,7 @@
       <c r="M376" s="16"/>
       <c r="N376" s="17"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -9993,7 +10086,7 @@
       <c r="M377" s="16"/>
       <c r="N377" s="17"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -10015,7 +10108,7 @@
       <c r="M378" s="16"/>
       <c r="N378" s="17"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -10037,7 +10130,7 @@
       <c r="M379" s="16"/>
       <c r="N379" s="17"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -10059,7 +10152,7 @@
       <c r="M380" s="16"/>
       <c r="N380" s="17"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -10081,7 +10174,7 @@
       <c r="M381" s="16"/>
       <c r="N381" s="17"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -10103,7 +10196,7 @@
       <c r="M382" s="16"/>
       <c r="N382" s="17"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -10125,7 +10218,7 @@
       <c r="M383" s="16"/>
       <c r="N383" s="17"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -10147,7 +10240,7 @@
       <c r="M384" s="16"/>
       <c r="N384" s="17"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -10169,7 +10262,7 @@
       <c r="M385" s="16"/>
       <c r="N385" s="17"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -10191,7 +10284,7 @@
       <c r="M386" s="16"/>
       <c r="N386" s="17"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -10213,7 +10306,7 @@
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -10235,7 +10328,7 @@
       <c r="M388" s="16"/>
       <c r="N388" s="17"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -10257,7 +10350,7 @@
       <c r="M389" s="16"/>
       <c r="N389" s="17"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -10279,7 +10372,7 @@
       <c r="M390" s="16"/>
       <c r="N390" s="17"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -10301,7 +10394,7 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -10323,7 +10416,7 @@
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -10345,7 +10438,7 @@
       <c r="M393" s="16"/>
       <c r="N393" s="17"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -10367,7 +10460,7 @@
       <c r="M394" s="16"/>
       <c r="N394" s="17"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -10389,7 +10482,7 @@
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -10411,7 +10504,7 @@
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -10433,7 +10526,7 @@
       <c r="M397" s="16"/>
       <c r="N397" s="17"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -10455,7 +10548,7 @@
       <c r="M398" s="16"/>
       <c r="N398" s="17"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -10477,7 +10570,7 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -10499,7 +10592,7 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D41B41064DFFF035/Desktop/pythonass/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A167787A-F9FD-4851-9173-7DAF0781A426}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B32CFCC-9E64-40E9-A4F3-CE5899F6A78F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -37,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -725,186 +720,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -916,7 +911,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -929,7 +924,7 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
@@ -947,7 +942,7 @@
       <c r="M1" s="24"/>
       <c r="N1" s="24"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -964,7 +959,7 @@
       </c>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -981,7 +976,7 @@
       </c>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
@@ -999,7 +994,7 @@
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
     </row>
-    <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1043,7 +1038,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1059,7 +1054,7 @@
       <c r="M6" s="11"/>
       <c r="N6" s="12"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>46255</v>
       </c>
@@ -1103,7 +1098,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
         <v>46256</v>
       </c>
@@ -1147,7 +1142,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>46257</v>
       </c>
@@ -1191,7 +1186,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>46258</v>
       </c>
@@ -1235,7 +1230,7 @@
       </c>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>46259</v>
       </c>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="N11" s="17"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>46260</v>
       </c>
@@ -1323,7 +1318,7 @@
       </c>
       <c r="N12" s="17"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>46261</v>
       </c>
@@ -1367,7 +1362,7 @@
       </c>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>46262</v>
       </c>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="N14" s="17"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>46263</v>
       </c>
@@ -1455,7 +1450,7 @@
       </c>
       <c r="N15" s="17"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>46264</v>
       </c>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="N16" s="17"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
         <v>46265</v>
       </c>
@@ -1543,7 +1538,7 @@
       </c>
       <c r="N17" s="17"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>46266</v>
       </c>
@@ -1587,7 +1582,7 @@
       </c>
       <c r="N18" s="17"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
         <v>46267</v>
       </c>
@@ -1631,7 +1626,7 @@
       </c>
       <c r="N19" s="17"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>46268</v>
       </c>
@@ -1675,7 +1670,7 @@
       </c>
       <c r="N20" s="17"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>46269</v>
       </c>
@@ -1719,7 +1714,7 @@
       </c>
       <c r="N21" s="17"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <v>46270</v>
       </c>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="N22" s="17"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>46271</v>
       </c>
@@ -1807,7 +1802,7 @@
       </c>
       <c r="N23" s="17"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
         <v>46272</v>
       </c>
@@ -1851,7 +1846,7 @@
       </c>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
         <v>46273</v>
       </c>
@@ -1895,7 +1890,7 @@
       </c>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <v>46274</v>
       </c>
@@ -1939,7 +1934,7 @@
       </c>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
         <v>46275</v>
       </c>
@@ -1985,7 +1980,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
         <v>46276</v>
       </c>
@@ -2031,7 +2026,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
         <v>46277</v>
       </c>
@@ -2077,7 +2072,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
         <v>46278</v>
       </c>
@@ -2123,7 +2118,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
         <v>46279</v>
       </c>
@@ -2167,7 +2162,7 @@
       </c>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
         <v>46280</v>
       </c>
@@ -2211,7 +2206,7 @@
       </c>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
         <v>46281</v>
       </c>
@@ -2255,7 +2250,7 @@
       </c>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
         <v>46282</v>
       </c>
@@ -2299,7 +2294,7 @@
       </c>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="13">
         <v>46283</v>
       </c>
@@ -2343,7 +2338,7 @@
       </c>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
         <v>46284</v>
       </c>
@@ -2387,7 +2382,7 @@
       </c>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="13">
         <v>46285</v>
       </c>
@@ -2430,7 +2425,7 @@
       </c>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="13">
         <v>46286</v>
       </c>
@@ -2474,7 +2469,7 @@
       </c>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
         <v>46287</v>
       </c>
@@ -2518,7 +2513,7 @@
       </c>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
         <v>46288</v>
       </c>
@@ -2562,7 +2557,7 @@
       </c>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="13">
         <v>46289</v>
       </c>
@@ -2606,7 +2601,7 @@
       </c>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
         <v>46290</v>
       </c>
@@ -2650,7 +2645,7 @@
       </c>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="13">
         <v>46291</v>
       </c>
@@ -2694,7 +2689,7 @@
       </c>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
         <v>46292</v>
       </c>
@@ -2738,7 +2733,7 @@
       </c>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="13">
         <v>46293</v>
       </c>
@@ -2782,51 +2777,95 @@
       </c>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B46" s="14">
+        <v>850</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>0</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>400</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B47" s="14">
+        <v>800</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>300</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2848,7 +2887,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2870,7 +2909,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2892,7 +2931,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2914,7 +2953,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2936,7 +2975,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2958,7 +2997,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2980,7 +3019,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -3002,7 +3041,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -3024,7 +3063,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -3046,7 +3085,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -3068,7 +3107,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -3090,7 +3129,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -3112,7 +3151,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -3134,7 +3173,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -3156,7 +3195,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -3178,7 +3217,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -3200,7 +3239,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -3222,7 +3261,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -3244,7 +3283,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -3266,7 +3305,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -3288,7 +3327,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -3310,7 +3349,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -3332,7 +3371,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -3354,7 +3393,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -3376,7 +3415,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -3398,7 +3437,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3420,7 +3459,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -3442,7 +3481,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -3464,7 +3503,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -3486,7 +3525,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -3508,7 +3547,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="17"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -3530,7 +3569,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="17"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -3552,7 +3591,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="17"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -3574,7 +3613,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="17"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -3596,7 +3635,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="17"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -3618,7 +3657,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="17"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -3640,7 +3679,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="17"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -3662,7 +3701,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="17"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -3684,7 +3723,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -3706,7 +3745,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -3728,7 +3767,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="17"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -3750,7 +3789,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="17"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -3772,7 +3811,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="17"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -3794,7 +3833,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="17"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -3816,7 +3855,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="17"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -3838,7 +3877,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="17"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -3860,7 +3899,7 @@
       <c r="M94" s="16"/>
       <c r="N94" s="17"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -3882,7 +3921,7 @@
       <c r="M95" s="16"/>
       <c r="N95" s="17"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -3904,7 +3943,7 @@
       <c r="M96" s="16"/>
       <c r="N96" s="17"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -3926,7 +3965,7 @@
       <c r="M97" s="16"/>
       <c r="N97" s="17"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -3948,7 +3987,7 @@
       <c r="M98" s="16"/>
       <c r="N98" s="17"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -3970,7 +4009,7 @@
       <c r="M99" s="16"/>
       <c r="N99" s="17"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -3992,7 +4031,7 @@
       <c r="M100" s="16"/>
       <c r="N100" s="17"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -4014,7 +4053,7 @@
       <c r="M101" s="16"/>
       <c r="N101" s="17"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -4036,7 +4075,7 @@
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -4058,7 +4097,7 @@
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -4080,7 +4119,7 @@
       <c r="M104" s="16"/>
       <c r="N104" s="17"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
@@ -4102,7 +4141,7 @@
       <c r="M105" s="16"/>
       <c r="N105" s="17"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
@@ -4124,7 +4163,7 @@
       <c r="M106" s="16"/>
       <c r="N106" s="17"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -4146,7 +4185,7 @@
       <c r="M107" s="16"/>
       <c r="N107" s="17"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -4168,7 +4207,7 @@
       <c r="M108" s="16"/>
       <c r="N108" s="17"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -4190,7 +4229,7 @@
       <c r="M109" s="16"/>
       <c r="N109" s="17"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -4212,7 +4251,7 @@
       <c r="M110" s="16"/>
       <c r="N110" s="17"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -4234,7 +4273,7 @@
       <c r="M111" s="16"/>
       <c r="N111" s="17"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -4256,7 +4295,7 @@
       <c r="M112" s="16"/>
       <c r="N112" s="17"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -4278,7 +4317,7 @@
       <c r="M113" s="16"/>
       <c r="N113" s="17"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
@@ -4300,7 +4339,7 @@
       <c r="M114" s="16"/>
       <c r="N114" s="17"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
@@ -4322,7 +4361,7 @@
       <c r="M115" s="16"/>
       <c r="N115" s="17"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -4344,7 +4383,7 @@
       <c r="M116" s="16"/>
       <c r="N116" s="17"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -4366,7 +4405,7 @@
       <c r="M117" s="16"/>
       <c r="N117" s="17"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -4388,7 +4427,7 @@
       <c r="M118" s="16"/>
       <c r="N118" s="17"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -4410,7 +4449,7 @@
       <c r="M119" s="16"/>
       <c r="N119" s="17"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -4432,7 +4471,7 @@
       <c r="M120" s="16"/>
       <c r="N120" s="17"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -4454,7 +4493,7 @@
       <c r="M121" s="16"/>
       <c r="N121" s="17"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -4476,7 +4515,7 @@
       <c r="M122" s="16"/>
       <c r="N122" s="17"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -4498,7 +4537,7 @@
       <c r="M123" s="16"/>
       <c r="N123" s="17"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -4520,7 +4559,7 @@
       <c r="M124" s="16"/>
       <c r="N124" s="17"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -4542,7 +4581,7 @@
       <c r="M125" s="16"/>
       <c r="N125" s="17"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -4564,7 +4603,7 @@
       <c r="M126" s="16"/>
       <c r="N126" s="17"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -4586,7 +4625,7 @@
       <c r="M127" s="16"/>
       <c r="N127" s="17"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -4608,7 +4647,7 @@
       <c r="M128" s="16"/>
       <c r="N128" s="17"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -4630,7 +4669,7 @@
       <c r="M129" s="16"/>
       <c r="N129" s="17"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -4652,7 +4691,7 @@
       <c r="M130" s="16"/>
       <c r="N130" s="17"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -4674,7 +4713,7 @@
       <c r="M131" s="16"/>
       <c r="N131" s="17"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -4696,7 +4735,7 @@
       <c r="M132" s="16"/>
       <c r="N132" s="17"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -4718,7 +4757,7 @@
       <c r="M133" s="16"/>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -4740,7 +4779,7 @@
       <c r="M134" s="16"/>
       <c r="N134" s="17"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -4762,7 +4801,7 @@
       <c r="M135" s="16"/>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -4784,7 +4823,7 @@
       <c r="M136" s="16"/>
       <c r="N136" s="17"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -4806,7 +4845,7 @@
       <c r="M137" s="16"/>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
@@ -4828,7 +4867,7 @@
       <c r="M138" s="16"/>
       <c r="N138" s="17"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -4850,7 +4889,7 @@
       <c r="M139" s="16"/>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -4872,7 +4911,7 @@
       <c r="M140" s="16"/>
       <c r="N140" s="17"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
@@ -4894,7 +4933,7 @@
       <c r="M141" s="16"/>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
@@ -4916,7 +4955,7 @@
       <c r="M142" s="16"/>
       <c r="N142" s="17"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
@@ -4938,7 +4977,7 @@
       <c r="M143" s="16"/>
       <c r="N143" s="17"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
@@ -4960,7 +4999,7 @@
       <c r="M144" s="16"/>
       <c r="N144" s="17"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -4982,7 +5021,7 @@
       <c r="M145" s="16"/>
       <c r="N145" s="17"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -5004,7 +5043,7 @@
       <c r="M146" s="16"/>
       <c r="N146" s="17"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -5026,7 +5065,7 @@
       <c r="M147" s="16"/>
       <c r="N147" s="17"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -5048,7 +5087,7 @@
       <c r="M148" s="16"/>
       <c r="N148" s="17"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
@@ -5070,7 +5109,7 @@
       <c r="M149" s="16"/>
       <c r="N149" s="17"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -5092,7 +5131,7 @@
       <c r="M150" s="16"/>
       <c r="N150" s="17"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -5114,7 +5153,7 @@
       <c r="M151" s="16"/>
       <c r="N151" s="17"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -5136,7 +5175,7 @@
       <c r="M152" s="16"/>
       <c r="N152" s="17"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -5158,7 +5197,7 @@
       <c r="M153" s="16"/>
       <c r="N153" s="17"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
@@ -5180,7 +5219,7 @@
       <c r="M154" s="16"/>
       <c r="N154" s="17"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
@@ -5202,7 +5241,7 @@
       <c r="M155" s="16"/>
       <c r="N155" s="17"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
@@ -5224,7 +5263,7 @@
       <c r="M156" s="16"/>
       <c r="N156" s="17"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
@@ -5246,7 +5285,7 @@
       <c r="M157" s="16"/>
       <c r="N157" s="17"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -5268,7 +5307,7 @@
       <c r="M158" s="16"/>
       <c r="N158" s="17"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -5290,7 +5329,7 @@
       <c r="M159" s="16"/>
       <c r="N159" s="17"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -5312,7 +5351,7 @@
       <c r="M160" s="16"/>
       <c r="N160" s="17"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -5334,7 +5373,7 @@
       <c r="M161" s="16"/>
       <c r="N161" s="17"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -5356,7 +5395,7 @@
       <c r="M162" s="16"/>
       <c r="N162" s="17"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -5378,7 +5417,7 @@
       <c r="M163" s="16"/>
       <c r="N163" s="17"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -5400,7 +5439,7 @@
       <c r="M164" s="16"/>
       <c r="N164" s="17"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
@@ -5422,7 +5461,7 @@
       <c r="M165" s="16"/>
       <c r="N165" s="17"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
@@ -5444,7 +5483,7 @@
       <c r="M166" s="16"/>
       <c r="N166" s="17"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -5466,7 +5505,7 @@
       <c r="M167" s="16"/>
       <c r="N167" s="17"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
@@ -5488,7 +5527,7 @@
       <c r="M168" s="16"/>
       <c r="N168" s="17"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
@@ -5510,7 +5549,7 @@
       <c r="M169" s="16"/>
       <c r="N169" s="17"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -5532,7 +5571,7 @@
       <c r="M170" s="16"/>
       <c r="N170" s="17"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -5554,7 +5593,7 @@
       <c r="M171" s="16"/>
       <c r="N171" s="17"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -5576,7 +5615,7 @@
       <c r="M172" s="16"/>
       <c r="N172" s="17"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -5598,7 +5637,7 @@
       <c r="M173" s="16"/>
       <c r="N173" s="17"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -5620,7 +5659,7 @@
       <c r="M174" s="16"/>
       <c r="N174" s="17"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -5642,7 +5681,7 @@
       <c r="M175" s="16"/>
       <c r="N175" s="17"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -5664,7 +5703,7 @@
       <c r="M176" s="16"/>
       <c r="N176" s="17"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -5686,7 +5725,7 @@
       <c r="M177" s="16"/>
       <c r="N177" s="17"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -5708,7 +5747,7 @@
       <c r="M178" s="16"/>
       <c r="N178" s="17"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -5730,7 +5769,7 @@
       <c r="M179" s="16"/>
       <c r="N179" s="17"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -5752,7 +5791,7 @@
       <c r="M180" s="16"/>
       <c r="N180" s="17"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -5774,7 +5813,7 @@
       <c r="M181" s="16"/>
       <c r="N181" s="17"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -5796,7 +5835,7 @@
       <c r="M182" s="16"/>
       <c r="N182" s="17"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -5818,7 +5857,7 @@
       <c r="M183" s="16"/>
       <c r="N183" s="17"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -5840,7 +5879,7 @@
       <c r="M184" s="16"/>
       <c r="N184" s="17"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -5862,7 +5901,7 @@
       <c r="M185" s="16"/>
       <c r="N185" s="17"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -5884,7 +5923,7 @@
       <c r="M186" s="16"/>
       <c r="N186" s="17"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -5906,7 +5945,7 @@
       <c r="M187" s="16"/>
       <c r="N187" s="17"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -5928,7 +5967,7 @@
       <c r="M188" s="16"/>
       <c r="N188" s="17"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -5950,7 +5989,7 @@
       <c r="M189" s="16"/>
       <c r="N189" s="17"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -5972,7 +6011,7 @@
       <c r="M190" s="16"/>
       <c r="N190" s="17"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -5994,7 +6033,7 @@
       <c r="M191" s="16"/>
       <c r="N191" s="17"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -6016,7 +6055,7 @@
       <c r="M192" s="16"/>
       <c r="N192" s="17"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -6038,7 +6077,7 @@
       <c r="M193" s="16"/>
       <c r="N193" s="17"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -6060,7 +6099,7 @@
       <c r="M194" s="16"/>
       <c r="N194" s="17"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -6082,7 +6121,7 @@
       <c r="M195" s="16"/>
       <c r="N195" s="17"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -6104,7 +6143,7 @@
       <c r="M196" s="16"/>
       <c r="N196" s="17"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -6126,7 +6165,7 @@
       <c r="M197" s="16"/>
       <c r="N197" s="17"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -6148,7 +6187,7 @@
       <c r="M198" s="16"/>
       <c r="N198" s="17"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -6170,7 +6209,7 @@
       <c r="M199" s="16"/>
       <c r="N199" s="17"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -6192,7 +6231,7 @@
       <c r="M200" s="16"/>
       <c r="N200" s="17"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -6214,7 +6253,7 @@
       <c r="M201" s="16"/>
       <c r="N201" s="17"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -6236,7 +6275,7 @@
       <c r="M202" s="16"/>
       <c r="N202" s="17"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -6258,7 +6297,7 @@
       <c r="M203" s="16"/>
       <c r="N203" s="17"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -6280,7 +6319,7 @@
       <c r="M204" s="16"/>
       <c r="N204" s="17"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -6302,7 +6341,7 @@
       <c r="M205" s="16"/>
       <c r="N205" s="17"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -6324,7 +6363,7 @@
       <c r="M206" s="16"/>
       <c r="N206" s="17"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -6346,7 +6385,7 @@
       <c r="M207" s="16"/>
       <c r="N207" s="17"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -6368,7 +6407,7 @@
       <c r="M208" s="16"/>
       <c r="N208" s="17"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -6390,7 +6429,7 @@
       <c r="M209" s="16"/>
       <c r="N209" s="17"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -6412,7 +6451,7 @@
       <c r="M210" s="16"/>
       <c r="N210" s="17"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -6434,7 +6473,7 @@
       <c r="M211" s="16"/>
       <c r="N211" s="17"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -6456,7 +6495,7 @@
       <c r="M212" s="16"/>
       <c r="N212" s="17"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -6478,7 +6517,7 @@
       <c r="M213" s="16"/>
       <c r="N213" s="17"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -6500,7 +6539,7 @@
       <c r="M214" s="16"/>
       <c r="N214" s="17"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -6522,7 +6561,7 @@
       <c r="M215" s="16"/>
       <c r="N215" s="17"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -6544,7 +6583,7 @@
       <c r="M216" s="16"/>
       <c r="N216" s="17"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -6566,7 +6605,7 @@
       <c r="M217" s="16"/>
       <c r="N217" s="17"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -6588,7 +6627,7 @@
       <c r="M218" s="16"/>
       <c r="N218" s="17"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -6610,7 +6649,7 @@
       <c r="M219" s="16"/>
       <c r="N219" s="17"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -6632,7 +6671,7 @@
       <c r="M220" s="16"/>
       <c r="N220" s="17"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -6654,7 +6693,7 @@
       <c r="M221" s="16"/>
       <c r="N221" s="17"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -6676,7 +6715,7 @@
       <c r="M222" s="16"/>
       <c r="N222" s="17"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -6698,7 +6737,7 @@
       <c r="M223" s="16"/>
       <c r="N223" s="17"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -6720,7 +6759,7 @@
       <c r="M224" s="16"/>
       <c r="N224" s="17"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -6742,7 +6781,7 @@
       <c r="M225" s="16"/>
       <c r="N225" s="17"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -6764,7 +6803,7 @@
       <c r="M226" s="16"/>
       <c r="N226" s="17"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -6786,7 +6825,7 @@
       <c r="M227" s="16"/>
       <c r="N227" s="17"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -6808,7 +6847,7 @@
       <c r="M228" s="16"/>
       <c r="N228" s="17"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -6830,7 +6869,7 @@
       <c r="M229" s="16"/>
       <c r="N229" s="17"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -6852,7 +6891,7 @@
       <c r="M230" s="16"/>
       <c r="N230" s="17"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -6874,7 +6913,7 @@
       <c r="M231" s="16"/>
       <c r="N231" s="17"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -6896,7 +6935,7 @@
       <c r="M232" s="16"/>
       <c r="N232" s="17"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6918,7 +6957,7 @@
       <c r="M233" s="16"/>
       <c r="N233" s="17"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -6940,7 +6979,7 @@
       <c r="M234" s="16"/>
       <c r="N234" s="17"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -6962,7 +7001,7 @@
       <c r="M235" s="16"/>
       <c r="N235" s="17"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -6984,7 +7023,7 @@
       <c r="M236" s="16"/>
       <c r="N236" s="17"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -7006,7 +7045,7 @@
       <c r="M237" s="16"/>
       <c r="N237" s="17"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -7028,7 +7067,7 @@
       <c r="M238" s="16"/>
       <c r="N238" s="17"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -7050,7 +7089,7 @@
       <c r="M239" s="16"/>
       <c r="N239" s="17"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -7072,7 +7111,7 @@
       <c r="M240" s="16"/>
       <c r="N240" s="17"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -7094,7 +7133,7 @@
       <c r="M241" s="16"/>
       <c r="N241" s="17"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -7116,7 +7155,7 @@
       <c r="M242" s="16"/>
       <c r="N242" s="17"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -7138,7 +7177,7 @@
       <c r="M243" s="16"/>
       <c r="N243" s="17"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -7160,7 +7199,7 @@
       <c r="M244" s="16"/>
       <c r="N244" s="17"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -7182,7 +7221,7 @@
       <c r="M245" s="16"/>
       <c r="N245" s="17"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -7204,7 +7243,7 @@
       <c r="M246" s="16"/>
       <c r="N246" s="17"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -7226,7 +7265,7 @@
       <c r="M247" s="16"/>
       <c r="N247" s="17"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -7248,7 +7287,7 @@
       <c r="M248" s="16"/>
       <c r="N248" s="17"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -7270,7 +7309,7 @@
       <c r="M249" s="16"/>
       <c r="N249" s="17"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -7292,7 +7331,7 @@
       <c r="M250" s="16"/>
       <c r="N250" s="17"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -7314,7 +7353,7 @@
       <c r="M251" s="16"/>
       <c r="N251" s="17"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -7336,7 +7375,7 @@
       <c r="M252" s="16"/>
       <c r="N252" s="17"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -7358,7 +7397,7 @@
       <c r="M253" s="16"/>
       <c r="N253" s="17"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -7380,7 +7419,7 @@
       <c r="M254" s="16"/>
       <c r="N254" s="17"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -7402,7 +7441,7 @@
       <c r="M255" s="16"/>
       <c r="N255" s="17"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -7424,7 +7463,7 @@
       <c r="M256" s="16"/>
       <c r="N256" s="17"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -7446,7 +7485,7 @@
       <c r="M257" s="16"/>
       <c r="N257" s="17"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -7468,7 +7507,7 @@
       <c r="M258" s="16"/>
       <c r="N258" s="17"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -7490,7 +7529,7 @@
       <c r="M259" s="16"/>
       <c r="N259" s="17"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -7512,7 +7551,7 @@
       <c r="M260" s="16"/>
       <c r="N260" s="17"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -7534,7 +7573,7 @@
       <c r="M261" s="16"/>
       <c r="N261" s="17"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -7556,7 +7595,7 @@
       <c r="M262" s="16"/>
       <c r="N262" s="17"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -7578,7 +7617,7 @@
       <c r="M263" s="16"/>
       <c r="N263" s="17"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -7600,7 +7639,7 @@
       <c r="M264" s="16"/>
       <c r="N264" s="17"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -7622,7 +7661,7 @@
       <c r="M265" s="16"/>
       <c r="N265" s="17"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -7644,7 +7683,7 @@
       <c r="M266" s="16"/>
       <c r="N266" s="17"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -7666,7 +7705,7 @@
       <c r="M267" s="16"/>
       <c r="N267" s="17"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -7688,7 +7727,7 @@
       <c r="M268" s="16"/>
       <c r="N268" s="17"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -7710,7 +7749,7 @@
       <c r="M269" s="16"/>
       <c r="N269" s="17"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -7732,7 +7771,7 @@
       <c r="M270" s="16"/>
       <c r="N270" s="17"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -7754,7 +7793,7 @@
       <c r="M271" s="16"/>
       <c r="N271" s="17"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -7776,7 +7815,7 @@
       <c r="M272" s="16"/>
       <c r="N272" s="17"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -7798,7 +7837,7 @@
       <c r="M273" s="16"/>
       <c r="N273" s="17"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -7820,7 +7859,7 @@
       <c r="M274" s="16"/>
       <c r="N274" s="17"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -7842,7 +7881,7 @@
       <c r="M275" s="16"/>
       <c r="N275" s="17"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -7864,7 +7903,7 @@
       <c r="M276" s="16"/>
       <c r="N276" s="17"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -7886,7 +7925,7 @@
       <c r="M277" s="16"/>
       <c r="N277" s="17"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -7908,7 +7947,7 @@
       <c r="M278" s="16"/>
       <c r="N278" s="17"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -7930,7 +7969,7 @@
       <c r="M279" s="16"/>
       <c r="N279" s="17"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -7952,7 +7991,7 @@
       <c r="M280" s="16"/>
       <c r="N280" s="17"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -7974,7 +8013,7 @@
       <c r="M281" s="16"/>
       <c r="N281" s="17"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -7996,7 +8035,7 @@
       <c r="M282" s="16"/>
       <c r="N282" s="17"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -8018,7 +8057,7 @@
       <c r="M283" s="16"/>
       <c r="N283" s="17"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -8040,7 +8079,7 @@
       <c r="M284" s="16"/>
       <c r="N284" s="17"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -8062,7 +8101,7 @@
       <c r="M285" s="16"/>
       <c r="N285" s="17"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -8084,7 +8123,7 @@
       <c r="M286" s="16"/>
       <c r="N286" s="17"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -8106,7 +8145,7 @@
       <c r="M287" s="16"/>
       <c r="N287" s="17"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -8128,7 +8167,7 @@
       <c r="M288" s="16"/>
       <c r="N288" s="17"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -8150,7 +8189,7 @@
       <c r="M289" s="16"/>
       <c r="N289" s="17"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -8172,7 +8211,7 @@
       <c r="M290" s="16"/>
       <c r="N290" s="17"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -8194,7 +8233,7 @@
       <c r="M291" s="16"/>
       <c r="N291" s="17"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -8216,7 +8255,7 @@
       <c r="M292" s="16"/>
       <c r="N292" s="17"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -8238,7 +8277,7 @@
       <c r="M293" s="16"/>
       <c r="N293" s="17"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -8260,7 +8299,7 @@
       <c r="M294" s="16"/>
       <c r="N294" s="17"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -8282,7 +8321,7 @@
       <c r="M295" s="16"/>
       <c r="N295" s="17"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -8304,7 +8343,7 @@
       <c r="M296" s="16"/>
       <c r="N296" s="17"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -8326,7 +8365,7 @@
       <c r="M297" s="16"/>
       <c r="N297" s="17"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -8348,7 +8387,7 @@
       <c r="M298" s="16"/>
       <c r="N298" s="17"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -8370,7 +8409,7 @@
       <c r="M299" s="16"/>
       <c r="N299" s="17"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -8392,7 +8431,7 @@
       <c r="M300" s="16"/>
       <c r="N300" s="17"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -8414,7 +8453,7 @@
       <c r="M301" s="16"/>
       <c r="N301" s="17"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -8436,7 +8475,7 @@
       <c r="M302" s="16"/>
       <c r="N302" s="17"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -8458,7 +8497,7 @@
       <c r="M303" s="16"/>
       <c r="N303" s="17"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -8480,7 +8519,7 @@
       <c r="M304" s="16"/>
       <c r="N304" s="17"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -8502,7 +8541,7 @@
       <c r="M305" s="16"/>
       <c r="N305" s="17"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -8524,7 +8563,7 @@
       <c r="M306" s="16"/>
       <c r="N306" s="17"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -8546,7 +8585,7 @@
       <c r="M307" s="16"/>
       <c r="N307" s="17"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -8568,7 +8607,7 @@
       <c r="M308" s="16"/>
       <c r="N308" s="17"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -8590,7 +8629,7 @@
       <c r="M309" s="16"/>
       <c r="N309" s="17"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -8612,7 +8651,7 @@
       <c r="M310" s="16"/>
       <c r="N310" s="17"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -8634,7 +8673,7 @@
       <c r="M311" s="16"/>
       <c r="N311" s="17"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -8656,7 +8695,7 @@
       <c r="M312" s="16"/>
       <c r="N312" s="17"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -8678,7 +8717,7 @@
       <c r="M313" s="16"/>
       <c r="N313" s="17"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -8700,7 +8739,7 @@
       <c r="M314" s="16"/>
       <c r="N314" s="17"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -8722,7 +8761,7 @@
       <c r="M315" s="16"/>
       <c r="N315" s="17"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -8744,7 +8783,7 @@
       <c r="M316" s="16"/>
       <c r="N316" s="17"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -8766,7 +8805,7 @@
       <c r="M317" s="16"/>
       <c r="N317" s="17"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -8788,7 +8827,7 @@
       <c r="M318" s="16"/>
       <c r="N318" s="17"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -8810,7 +8849,7 @@
       <c r="M319" s="16"/>
       <c r="N319" s="17"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -8832,7 +8871,7 @@
       <c r="M320" s="16"/>
       <c r="N320" s="17"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -8854,7 +8893,7 @@
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -8876,7 +8915,7 @@
       <c r="M322" s="16"/>
       <c r="N322" s="17"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -8898,7 +8937,7 @@
       <c r="M323" s="16"/>
       <c r="N323" s="17"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -8920,7 +8959,7 @@
       <c r="M324" s="16"/>
       <c r="N324" s="17"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -8942,7 +8981,7 @@
       <c r="M325" s="16"/>
       <c r="N325" s="17"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -8964,7 +9003,7 @@
       <c r="M326" s="16"/>
       <c r="N326" s="17"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -8986,7 +9025,7 @@
       <c r="M327" s="16"/>
       <c r="N327" s="17"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -9008,7 +9047,7 @@
       <c r="M328" s="16"/>
       <c r="N328" s="17"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -9030,7 +9069,7 @@
       <c r="M329" s="16"/>
       <c r="N329" s="17"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -9052,7 +9091,7 @@
       <c r="M330" s="16"/>
       <c r="N330" s="17"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -9074,7 +9113,7 @@
       <c r="M331" s="16"/>
       <c r="N331" s="17"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -9096,7 +9135,7 @@
       <c r="M332" s="16"/>
       <c r="N332" s="17"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -9118,7 +9157,7 @@
       <c r="M333" s="16"/>
       <c r="N333" s="17"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -9140,7 +9179,7 @@
       <c r="M334" s="16"/>
       <c r="N334" s="17"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -9162,7 +9201,7 @@
       <c r="M335" s="16"/>
       <c r="N335" s="17"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -9184,7 +9223,7 @@
       <c r="M336" s="16"/>
       <c r="N336" s="17"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -9206,7 +9245,7 @@
       <c r="M337" s="16"/>
       <c r="N337" s="17"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -9228,7 +9267,7 @@
       <c r="M338" s="16"/>
       <c r="N338" s="17"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -9250,7 +9289,7 @@
       <c r="M339" s="16"/>
       <c r="N339" s="17"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -9272,7 +9311,7 @@
       <c r="M340" s="16"/>
       <c r="N340" s="17"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -9294,7 +9333,7 @@
       <c r="M341" s="16"/>
       <c r="N341" s="17"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -9316,7 +9355,7 @@
       <c r="M342" s="16"/>
       <c r="N342" s="17"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -9338,7 +9377,7 @@
       <c r="M343" s="16"/>
       <c r="N343" s="17"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -9360,7 +9399,7 @@
       <c r="M344" s="16"/>
       <c r="N344" s="17"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -9382,7 +9421,7 @@
       <c r="M345" s="16"/>
       <c r="N345" s="17"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -9404,7 +9443,7 @@
       <c r="M346" s="16"/>
       <c r="N346" s="17"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -9426,7 +9465,7 @@
       <c r="M347" s="16"/>
       <c r="N347" s="17"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -9448,7 +9487,7 @@
       <c r="M348" s="16"/>
       <c r="N348" s="17"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -9470,7 +9509,7 @@
       <c r="M349" s="16"/>
       <c r="N349" s="17"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -9492,7 +9531,7 @@
       <c r="M350" s="16"/>
       <c r="N350" s="17"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -9514,7 +9553,7 @@
       <c r="M351" s="16"/>
       <c r="N351" s="17"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -9536,7 +9575,7 @@
       <c r="M352" s="16"/>
       <c r="N352" s="17"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -9558,7 +9597,7 @@
       <c r="M353" s="16"/>
       <c r="N353" s="17"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -9580,7 +9619,7 @@
       <c r="M354" s="16"/>
       <c r="N354" s="17"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -9602,7 +9641,7 @@
       <c r="M355" s="16"/>
       <c r="N355" s="17"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -9624,7 +9663,7 @@
       <c r="M356" s="16"/>
       <c r="N356" s="17"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -9646,7 +9685,7 @@
       <c r="M357" s="16"/>
       <c r="N357" s="17"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -9668,7 +9707,7 @@
       <c r="M358" s="16"/>
       <c r="N358" s="17"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -9690,7 +9729,7 @@
       <c r="M359" s="16"/>
       <c r="N359" s="17"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -9712,7 +9751,7 @@
       <c r="M360" s="16"/>
       <c r="N360" s="17"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -9734,7 +9773,7 @@
       <c r="M361" s="16"/>
       <c r="N361" s="17"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -9756,7 +9795,7 @@
       <c r="M362" s="16"/>
       <c r="N362" s="17"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -9778,7 +9817,7 @@
       <c r="M363" s="16"/>
       <c r="N363" s="17"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -9800,7 +9839,7 @@
       <c r="M364" s="16"/>
       <c r="N364" s="17"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -9822,7 +9861,7 @@
       <c r="M365" s="16"/>
       <c r="N365" s="17"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -9844,7 +9883,7 @@
       <c r="M366" s="16"/>
       <c r="N366" s="17"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -9866,7 +9905,7 @@
       <c r="M367" s="16"/>
       <c r="N367" s="17"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -9888,7 +9927,7 @@
       <c r="M368" s="16"/>
       <c r="N368" s="17"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -9910,7 +9949,7 @@
       <c r="M369" s="16"/>
       <c r="N369" s="17"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -9932,7 +9971,7 @@
       <c r="M370" s="16"/>
       <c r="N370" s="17"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -9954,7 +9993,7 @@
       <c r="M371" s="16"/>
       <c r="N371" s="17"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -9976,7 +10015,7 @@
       <c r="M372" s="16"/>
       <c r="N372" s="17"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -9998,7 +10037,7 @@
       <c r="M373" s="16"/>
       <c r="N373" s="17"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -10020,7 +10059,7 @@
       <c r="M374" s="16"/>
       <c r="N374" s="17"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -10042,7 +10081,7 @@
       <c r="M375" s="16"/>
       <c r="N375" s="17"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -10064,7 +10103,7 @@
       <c r="M376" s="16"/>
       <c r="N376" s="17"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -10086,7 +10125,7 @@
       <c r="M377" s="16"/>
       <c r="N377" s="17"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -10108,7 +10147,7 @@
       <c r="M378" s="16"/>
       <c r="N378" s="17"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -10130,7 +10169,7 @@
       <c r="M379" s="16"/>
       <c r="N379" s="17"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -10152,7 +10191,7 @@
       <c r="M380" s="16"/>
       <c r="N380" s="17"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -10174,7 +10213,7 @@
       <c r="M381" s="16"/>
       <c r="N381" s="17"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -10196,7 +10235,7 @@
       <c r="M382" s="16"/>
       <c r="N382" s="17"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -10218,7 +10257,7 @@
       <c r="M383" s="16"/>
       <c r="N383" s="17"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -10240,7 +10279,7 @@
       <c r="M384" s="16"/>
       <c r="N384" s="17"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -10262,7 +10301,7 @@
       <c r="M385" s="16"/>
       <c r="N385" s="17"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -10284,7 +10323,7 @@
       <c r="M386" s="16"/>
       <c r="N386" s="17"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -10306,7 +10345,7 @@
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -10328,7 +10367,7 @@
       <c r="M388" s="16"/>
       <c r="N388" s="17"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -10350,7 +10389,7 @@
       <c r="M389" s="16"/>
       <c r="N389" s="17"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -10372,7 +10411,7 @@
       <c r="M390" s="16"/>
       <c r="N390" s="17"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -10394,7 +10433,7 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -10416,7 +10455,7 @@
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -10438,7 +10477,7 @@
       <c r="M393" s="16"/>
       <c r="N393" s="17"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -10460,7 +10499,7 @@
       <c r="M394" s="16"/>
       <c r="N394" s="17"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -10482,7 +10521,7 @@
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -10504,7 +10543,7 @@
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -10526,7 +10565,7 @@
       <c r="M397" s="16"/>
       <c r="N397" s="17"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -10548,7 +10587,7 @@
       <c r="M398" s="16"/>
       <c r="N398" s="17"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -10570,7 +10609,7 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -10592,7 +10631,7 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41b41064dfff035/Desktop/pythonass/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D41B41064DFFF035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B32CFCC-9E64-40E9-A4F3-CE5899F6A78F}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE8B3A85-38F4-4DDE-B908-C6E276138B1A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -720,186 +725,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="23" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -911,7 +916,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -924,7 +929,7 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
@@ -942,7 +947,7 @@
       <c r="M1" s="24"/>
       <c r="N1" s="24"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -959,7 +964,7 @@
       </c>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -976,7 +981,7 @@
       </c>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
@@ -994,7 +999,7 @@
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1038,7 +1043,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1054,7 +1059,7 @@
       <c r="M6" s="11"/>
       <c r="N6" s="12"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="18">
         <v>46255</v>
       </c>
@@ -1098,7 +1103,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="18">
         <v>46256</v>
       </c>
@@ -1142,7 +1147,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="18">
         <v>46257</v>
       </c>
@@ -1186,7 +1191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
         <v>46258</v>
       </c>
@@ -1230,7 +1235,7 @@
       </c>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
         <v>46259</v>
       </c>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="N11" s="17"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
         <v>46260</v>
       </c>
@@ -1318,7 +1323,7 @@
       </c>
       <c r="N12" s="17"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
         <v>46261</v>
       </c>
@@ -1362,7 +1367,7 @@
       </c>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
         <v>46262</v>
       </c>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="N14" s="17"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13">
         <v>46263</v>
       </c>
@@ -1450,7 +1455,7 @@
       </c>
       <c r="N15" s="17"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13">
         <v>46264</v>
       </c>
@@ -1494,7 +1499,7 @@
       </c>
       <c r="N16" s="17"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13">
         <v>46265</v>
       </c>
@@ -1538,7 +1543,7 @@
       </c>
       <c r="N17" s="17"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
         <v>46266</v>
       </c>
@@ -1582,7 +1587,7 @@
       </c>
       <c r="N18" s="17"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">
         <v>46267</v>
       </c>
@@ -1626,7 +1631,7 @@
       </c>
       <c r="N19" s="17"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
         <v>46268</v>
       </c>
@@ -1670,7 +1675,7 @@
       </c>
       <c r="N20" s="17"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
         <v>46269</v>
       </c>
@@ -1714,7 +1719,7 @@
       </c>
       <c r="N21" s="17"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
         <v>46270</v>
       </c>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="N22" s="17"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13">
         <v>46271</v>
       </c>
@@ -1802,7 +1807,7 @@
       </c>
       <c r="N23" s="17"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
         <v>46272</v>
       </c>
@@ -1846,7 +1851,7 @@
       </c>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13">
         <v>46273</v>
       </c>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
         <v>46274</v>
       </c>
@@ -1934,7 +1939,7 @@
       </c>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">
         <v>46275</v>
       </c>
@@ -1980,7 +1985,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
         <v>46276</v>
       </c>
@@ -2026,7 +2031,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
         <v>46277</v>
       </c>
@@ -2072,7 +2077,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
         <v>46278</v>
       </c>
@@ -2118,7 +2123,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
         <v>46279</v>
       </c>
@@ -2162,7 +2167,7 @@
       </c>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
         <v>46280</v>
       </c>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13">
         <v>46281</v>
       </c>
@@ -2250,7 +2255,7 @@
       </c>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13">
         <v>46282</v>
       </c>
@@ -2294,7 +2299,7 @@
       </c>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
         <v>46283</v>
       </c>
@@ -2338,7 +2343,7 @@
       </c>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
         <v>46284</v>
       </c>
@@ -2382,7 +2387,7 @@
       </c>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13">
         <v>46285</v>
       </c>
@@ -2425,7 +2430,7 @@
       </c>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13">
         <v>46286</v>
       </c>
@@ -2469,7 +2474,7 @@
       </c>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13">
         <v>46287</v>
       </c>
@@ -2513,7 +2518,7 @@
       </c>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="13">
         <v>46288</v>
       </c>
@@ -2557,7 +2562,7 @@
       </c>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13">
         <v>46289</v>
       </c>
@@ -2601,7 +2606,7 @@
       </c>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13">
         <v>46290</v>
       </c>
@@ -2645,7 +2650,7 @@
       </c>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="13">
         <v>46291</v>
       </c>
@@ -2689,7 +2694,7 @@
       </c>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="13">
         <v>46292</v>
       </c>
@@ -2733,7 +2738,7 @@
       </c>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13">
         <v>46293</v>
       </c>
@@ -2777,7 +2782,7 @@
       </c>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="13">
         <v>46294</v>
       </c>
@@ -2821,7 +2826,7 @@
       </c>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="13">
         <v>46295</v>
       </c>
@@ -2865,52 +2870,98 @@
       </c>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A48" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B48" s="14">
+        <v>750</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>0</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>300</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A49" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B49" s="14">
+        <v>700</v>
+      </c>
+      <c r="C49" s="14">
+        <v>60</v>
+      </c>
+      <c r="D49" s="14">
+        <v>30</v>
+      </c>
+      <c r="E49" s="14">
+        <v>50</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>350</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="13"/>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A50" s="13">
+        <v>46298</v>
+      </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2931,8 +2982,10 @@
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A51" s="13">
+        <v>46299</v>
+      </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2953,8 +3006,10 @@
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="13"/>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A52" s="13">
+        <v>46300</v>
+      </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2975,8 +3030,10 @@
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="13"/>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A53" s="13">
+        <v>46301</v>
+      </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -2997,7 +3054,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -3019,7 +3076,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -3041,7 +3098,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -3063,7 +3120,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -3085,7 +3142,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -3107,7 +3164,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -3129,7 +3186,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -3151,7 +3208,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -3173,7 +3230,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -3195,7 +3252,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -3217,7 +3274,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -3239,7 +3296,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -3261,7 +3318,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -3283,7 +3340,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -3305,7 +3362,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -3327,7 +3384,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -3349,7 +3406,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -3371,7 +3428,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -3393,7 +3450,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -3415,7 +3472,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -3437,7 +3494,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3459,7 +3516,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -3481,7 +3538,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -3503,7 +3560,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -3525,7 +3582,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -3547,7 +3604,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="17"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -3569,7 +3626,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="17"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -3591,7 +3648,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="17"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -3613,7 +3670,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="17"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -3635,7 +3692,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="17"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -3657,7 +3714,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="17"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -3679,7 +3736,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="17"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -3701,7 +3758,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="17"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -3723,7 +3780,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -3745,7 +3802,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -3767,7 +3824,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="17"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -3789,7 +3846,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="17"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -3811,7 +3868,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="17"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -3833,7 +3890,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="17"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -3855,7 +3912,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="17"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -3877,7 +3934,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="17"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -3899,7 +3956,7 @@
       <c r="M94" s="16"/>
       <c r="N94" s="17"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -3921,7 +3978,7 @@
       <c r="M95" s="16"/>
       <c r="N95" s="17"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -3943,7 +4000,7 @@
       <c r="M96" s="16"/>
       <c r="N96" s="17"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -3965,7 +4022,7 @@
       <c r="M97" s="16"/>
       <c r="N97" s="17"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -3987,7 +4044,7 @@
       <c r="M98" s="16"/>
       <c r="N98" s="17"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -4009,7 +4066,7 @@
       <c r="M99" s="16"/>
       <c r="N99" s="17"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -4031,7 +4088,7 @@
       <c r="M100" s="16"/>
       <c r="N100" s="17"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -4053,7 +4110,7 @@
       <c r="M101" s="16"/>
       <c r="N101" s="17"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -4075,7 +4132,7 @@
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -4097,7 +4154,7 @@
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -4119,7 +4176,7 @@
       <c r="M104" s="16"/>
       <c r="N104" s="17"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
@@ -4141,7 +4198,7 @@
       <c r="M105" s="16"/>
       <c r="N105" s="17"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
@@ -4163,7 +4220,7 @@
       <c r="M106" s="16"/>
       <c r="N106" s="17"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -4185,7 +4242,7 @@
       <c r="M107" s="16"/>
       <c r="N107" s="17"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -4207,7 +4264,7 @@
       <c r="M108" s="16"/>
       <c r="N108" s="17"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -4229,7 +4286,7 @@
       <c r="M109" s="16"/>
       <c r="N109" s="17"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -4251,7 +4308,7 @@
       <c r="M110" s="16"/>
       <c r="N110" s="17"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -4273,7 +4330,7 @@
       <c r="M111" s="16"/>
       <c r="N111" s="17"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -4295,7 +4352,7 @@
       <c r="M112" s="16"/>
       <c r="N112" s="17"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -4317,7 +4374,7 @@
       <c r="M113" s="16"/>
       <c r="N113" s="17"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
@@ -4339,7 +4396,7 @@
       <c r="M114" s="16"/>
       <c r="N114" s="17"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
@@ -4361,7 +4418,7 @@
       <c r="M115" s="16"/>
       <c r="N115" s="17"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -4383,7 +4440,7 @@
       <c r="M116" s="16"/>
       <c r="N116" s="17"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -4405,7 +4462,7 @@
       <c r="M117" s="16"/>
       <c r="N117" s="17"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -4427,7 +4484,7 @@
       <c r="M118" s="16"/>
       <c r="N118" s="17"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -4449,7 +4506,7 @@
       <c r="M119" s="16"/>
       <c r="N119" s="17"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -4471,7 +4528,7 @@
       <c r="M120" s="16"/>
       <c r="N120" s="17"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -4493,7 +4550,7 @@
       <c r="M121" s="16"/>
       <c r="N121" s="17"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -4515,7 +4572,7 @@
       <c r="M122" s="16"/>
       <c r="N122" s="17"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -4537,7 +4594,7 @@
       <c r="M123" s="16"/>
       <c r="N123" s="17"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -4559,7 +4616,7 @@
       <c r="M124" s="16"/>
       <c r="N124" s="17"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -4581,7 +4638,7 @@
       <c r="M125" s="16"/>
       <c r="N125" s="17"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -4603,7 +4660,7 @@
       <c r="M126" s="16"/>
       <c r="N126" s="17"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -4625,7 +4682,7 @@
       <c r="M127" s="16"/>
       <c r="N127" s="17"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -4647,7 +4704,7 @@
       <c r="M128" s="16"/>
       <c r="N128" s="17"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -4669,7 +4726,7 @@
       <c r="M129" s="16"/>
       <c r="N129" s="17"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -4691,7 +4748,7 @@
       <c r="M130" s="16"/>
       <c r="N130" s="17"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -4713,7 +4770,7 @@
       <c r="M131" s="16"/>
       <c r="N131" s="17"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -4735,7 +4792,7 @@
       <c r="M132" s="16"/>
       <c r="N132" s="17"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -4757,7 +4814,7 @@
       <c r="M133" s="16"/>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -4779,7 +4836,7 @@
       <c r="M134" s="16"/>
       <c r="N134" s="17"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -4801,7 +4858,7 @@
       <c r="M135" s="16"/>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -4823,7 +4880,7 @@
       <c r="M136" s="16"/>
       <c r="N136" s="17"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -4845,7 +4902,7 @@
       <c r="M137" s="16"/>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
@@ -4867,7 +4924,7 @@
       <c r="M138" s="16"/>
       <c r="N138" s="17"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -4889,7 +4946,7 @@
       <c r="M139" s="16"/>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -4911,7 +4968,7 @@
       <c r="M140" s="16"/>
       <c r="N140" s="17"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
@@ -4933,7 +4990,7 @@
       <c r="M141" s="16"/>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
@@ -4955,7 +5012,7 @@
       <c r="M142" s="16"/>
       <c r="N142" s="17"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
@@ -4977,7 +5034,7 @@
       <c r="M143" s="16"/>
       <c r="N143" s="17"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
@@ -4999,7 +5056,7 @@
       <c r="M144" s="16"/>
       <c r="N144" s="17"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -5021,7 +5078,7 @@
       <c r="M145" s="16"/>
       <c r="N145" s="17"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -5043,7 +5100,7 @@
       <c r="M146" s="16"/>
       <c r="N146" s="17"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -5065,7 +5122,7 @@
       <c r="M147" s="16"/>
       <c r="N147" s="17"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -5087,7 +5144,7 @@
       <c r="M148" s="16"/>
       <c r="N148" s="17"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
@@ -5109,7 +5166,7 @@
       <c r="M149" s="16"/>
       <c r="N149" s="17"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -5131,7 +5188,7 @@
       <c r="M150" s="16"/>
       <c r="N150" s="17"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -5153,7 +5210,7 @@
       <c r="M151" s="16"/>
       <c r="N151" s="17"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -5175,7 +5232,7 @@
       <c r="M152" s="16"/>
       <c r="N152" s="17"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -5197,7 +5254,7 @@
       <c r="M153" s="16"/>
       <c r="N153" s="17"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
@@ -5219,7 +5276,7 @@
       <c r="M154" s="16"/>
       <c r="N154" s="17"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
@@ -5241,7 +5298,7 @@
       <c r="M155" s="16"/>
       <c r="N155" s="17"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
@@ -5263,7 +5320,7 @@
       <c r="M156" s="16"/>
       <c r="N156" s="17"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
@@ -5285,7 +5342,7 @@
       <c r="M157" s="16"/>
       <c r="N157" s="17"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -5307,7 +5364,7 @@
       <c r="M158" s="16"/>
       <c r="N158" s="17"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -5329,7 +5386,7 @@
       <c r="M159" s="16"/>
       <c r="N159" s="17"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -5351,7 +5408,7 @@
       <c r="M160" s="16"/>
       <c r="N160" s="17"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -5373,7 +5430,7 @@
       <c r="M161" s="16"/>
       <c r="N161" s="17"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -5395,7 +5452,7 @@
       <c r="M162" s="16"/>
       <c r="N162" s="17"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -5417,7 +5474,7 @@
       <c r="M163" s="16"/>
       <c r="N163" s="17"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -5439,7 +5496,7 @@
       <c r="M164" s="16"/>
       <c r="N164" s="17"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
@@ -5461,7 +5518,7 @@
       <c r="M165" s="16"/>
       <c r="N165" s="17"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
@@ -5483,7 +5540,7 @@
       <c r="M166" s="16"/>
       <c r="N166" s="17"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -5505,7 +5562,7 @@
       <c r="M167" s="16"/>
       <c r="N167" s="17"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
@@ -5527,7 +5584,7 @@
       <c r="M168" s="16"/>
       <c r="N168" s="17"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
@@ -5549,7 +5606,7 @@
       <c r="M169" s="16"/>
       <c r="N169" s="17"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -5571,7 +5628,7 @@
       <c r="M170" s="16"/>
       <c r="N170" s="17"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -5593,7 +5650,7 @@
       <c r="M171" s="16"/>
       <c r="N171" s="17"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -5615,7 +5672,7 @@
       <c r="M172" s="16"/>
       <c r="N172" s="17"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -5637,7 +5694,7 @@
       <c r="M173" s="16"/>
       <c r="N173" s="17"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -5659,7 +5716,7 @@
       <c r="M174" s="16"/>
       <c r="N174" s="17"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -5681,7 +5738,7 @@
       <c r="M175" s="16"/>
       <c r="N175" s="17"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -5703,7 +5760,7 @@
       <c r="M176" s="16"/>
       <c r="N176" s="17"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -5725,7 +5782,7 @@
       <c r="M177" s="16"/>
       <c r="N177" s="17"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -5747,7 +5804,7 @@
       <c r="M178" s="16"/>
       <c r="N178" s="17"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -5769,7 +5826,7 @@
       <c r="M179" s="16"/>
       <c r="N179" s="17"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -5791,7 +5848,7 @@
       <c r="M180" s="16"/>
       <c r="N180" s="17"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -5813,7 +5870,7 @@
       <c r="M181" s="16"/>
       <c r="N181" s="17"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -5835,7 +5892,7 @@
       <c r="M182" s="16"/>
       <c r="N182" s="17"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -5857,7 +5914,7 @@
       <c r="M183" s="16"/>
       <c r="N183" s="17"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -5879,7 +5936,7 @@
       <c r="M184" s="16"/>
       <c r="N184" s="17"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -5901,7 +5958,7 @@
       <c r="M185" s="16"/>
       <c r="N185" s="17"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -5923,7 +5980,7 @@
       <c r="M186" s="16"/>
       <c r="N186" s="17"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -5945,7 +6002,7 @@
       <c r="M187" s="16"/>
       <c r="N187" s="17"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -5967,7 +6024,7 @@
       <c r="M188" s="16"/>
       <c r="N188" s="17"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -5989,7 +6046,7 @@
       <c r="M189" s="16"/>
       <c r="N189" s="17"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -6011,7 +6068,7 @@
       <c r="M190" s="16"/>
       <c r="N190" s="17"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -6033,7 +6090,7 @@
       <c r="M191" s="16"/>
       <c r="N191" s="17"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -6055,7 +6112,7 @@
       <c r="M192" s="16"/>
       <c r="N192" s="17"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -6077,7 +6134,7 @@
       <c r="M193" s="16"/>
       <c r="N193" s="17"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -6099,7 +6156,7 @@
       <c r="M194" s="16"/>
       <c r="N194" s="17"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -6121,7 +6178,7 @@
       <c r="M195" s="16"/>
       <c r="N195" s="17"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -6143,7 +6200,7 @@
       <c r="M196" s="16"/>
       <c r="N196" s="17"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -6165,7 +6222,7 @@
       <c r="M197" s="16"/>
       <c r="N197" s="17"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -6187,7 +6244,7 @@
       <c r="M198" s="16"/>
       <c r="N198" s="17"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -6209,7 +6266,7 @@
       <c r="M199" s="16"/>
       <c r="N199" s="17"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -6231,7 +6288,7 @@
       <c r="M200" s="16"/>
       <c r="N200" s="17"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -6253,7 +6310,7 @@
       <c r="M201" s="16"/>
       <c r="N201" s="17"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -6275,7 +6332,7 @@
       <c r="M202" s="16"/>
       <c r="N202" s="17"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -6297,7 +6354,7 @@
       <c r="M203" s="16"/>
       <c r="N203" s="17"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -6319,7 +6376,7 @@
       <c r="M204" s="16"/>
       <c r="N204" s="17"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -6341,7 +6398,7 @@
       <c r="M205" s="16"/>
       <c r="N205" s="17"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -6363,7 +6420,7 @@
       <c r="M206" s="16"/>
       <c r="N206" s="17"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -6385,7 +6442,7 @@
       <c r="M207" s="16"/>
       <c r="N207" s="17"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -6407,7 +6464,7 @@
       <c r="M208" s="16"/>
       <c r="N208" s="17"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -6429,7 +6486,7 @@
       <c r="M209" s="16"/>
       <c r="N209" s="17"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -6451,7 +6508,7 @@
       <c r="M210" s="16"/>
       <c r="N210" s="17"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -6473,7 +6530,7 @@
       <c r="M211" s="16"/>
       <c r="N211" s="17"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -6495,7 +6552,7 @@
       <c r="M212" s="16"/>
       <c r="N212" s="17"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -6517,7 +6574,7 @@
       <c r="M213" s="16"/>
       <c r="N213" s="17"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -6539,7 +6596,7 @@
       <c r="M214" s="16"/>
       <c r="N214" s="17"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -6561,7 +6618,7 @@
       <c r="M215" s="16"/>
       <c r="N215" s="17"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -6583,7 +6640,7 @@
       <c r="M216" s="16"/>
       <c r="N216" s="17"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -6605,7 +6662,7 @@
       <c r="M217" s="16"/>
       <c r="N217" s="17"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -6627,7 +6684,7 @@
       <c r="M218" s="16"/>
       <c r="N218" s="17"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -6649,7 +6706,7 @@
       <c r="M219" s="16"/>
       <c r="N219" s="17"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -6671,7 +6728,7 @@
       <c r="M220" s="16"/>
       <c r="N220" s="17"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -6693,7 +6750,7 @@
       <c r="M221" s="16"/>
       <c r="N221" s="17"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -6715,7 +6772,7 @@
       <c r="M222" s="16"/>
       <c r="N222" s="17"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -6737,7 +6794,7 @@
       <c r="M223" s="16"/>
       <c r="N223" s="17"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -6759,7 +6816,7 @@
       <c r="M224" s="16"/>
       <c r="N224" s="17"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -6781,7 +6838,7 @@
       <c r="M225" s="16"/>
       <c r="N225" s="17"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -6803,7 +6860,7 @@
       <c r="M226" s="16"/>
       <c r="N226" s="17"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -6825,7 +6882,7 @@
       <c r="M227" s="16"/>
       <c r="N227" s="17"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -6847,7 +6904,7 @@
       <c r="M228" s="16"/>
       <c r="N228" s="17"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -6869,7 +6926,7 @@
       <c r="M229" s="16"/>
       <c r="N229" s="17"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -6891,7 +6948,7 @@
       <c r="M230" s="16"/>
       <c r="N230" s="17"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -6913,7 +6970,7 @@
       <c r="M231" s="16"/>
       <c r="N231" s="17"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -6935,7 +6992,7 @@
       <c r="M232" s="16"/>
       <c r="N232" s="17"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6957,7 +7014,7 @@
       <c r="M233" s="16"/>
       <c r="N233" s="17"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -6979,7 +7036,7 @@
       <c r="M234" s="16"/>
       <c r="N234" s="17"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -7001,7 +7058,7 @@
       <c r="M235" s="16"/>
       <c r="N235" s="17"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -7023,7 +7080,7 @@
       <c r="M236" s="16"/>
       <c r="N236" s="17"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -7045,7 +7102,7 @@
       <c r="M237" s="16"/>
       <c r="N237" s="17"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -7067,7 +7124,7 @@
       <c r="M238" s="16"/>
       <c r="N238" s="17"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -7089,7 +7146,7 @@
       <c r="M239" s="16"/>
       <c r="N239" s="17"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -7111,7 +7168,7 @@
       <c r="M240" s="16"/>
       <c r="N240" s="17"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -7133,7 +7190,7 @@
       <c r="M241" s="16"/>
       <c r="N241" s="17"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -7155,7 +7212,7 @@
       <c r="M242" s="16"/>
       <c r="N242" s="17"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -7177,7 +7234,7 @@
       <c r="M243" s="16"/>
       <c r="N243" s="17"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -7199,7 +7256,7 @@
       <c r="M244" s="16"/>
       <c r="N244" s="17"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -7221,7 +7278,7 @@
       <c r="M245" s="16"/>
       <c r="N245" s="17"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -7243,7 +7300,7 @@
       <c r="M246" s="16"/>
       <c r="N246" s="17"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -7265,7 +7322,7 @@
       <c r="M247" s="16"/>
       <c r="N247" s="17"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -7287,7 +7344,7 @@
       <c r="M248" s="16"/>
       <c r="N248" s="17"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -7309,7 +7366,7 @@
       <c r="M249" s="16"/>
       <c r="N249" s="17"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -7331,7 +7388,7 @@
       <c r="M250" s="16"/>
       <c r="N250" s="17"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -7353,7 +7410,7 @@
       <c r="M251" s="16"/>
       <c r="N251" s="17"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -7375,7 +7432,7 @@
       <c r="M252" s="16"/>
       <c r="N252" s="17"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -7397,7 +7454,7 @@
       <c r="M253" s="16"/>
       <c r="N253" s="17"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -7419,7 +7476,7 @@
       <c r="M254" s="16"/>
       <c r="N254" s="17"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -7441,7 +7498,7 @@
       <c r="M255" s="16"/>
       <c r="N255" s="17"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -7463,7 +7520,7 @@
       <c r="M256" s="16"/>
       <c r="N256" s="17"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -7485,7 +7542,7 @@
       <c r="M257" s="16"/>
       <c r="N257" s="17"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -7507,7 +7564,7 @@
       <c r="M258" s="16"/>
       <c r="N258" s="17"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -7529,7 +7586,7 @@
       <c r="M259" s="16"/>
       <c r="N259" s="17"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -7551,7 +7608,7 @@
       <c r="M260" s="16"/>
       <c r="N260" s="17"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -7573,7 +7630,7 @@
       <c r="M261" s="16"/>
       <c r="N261" s="17"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -7595,7 +7652,7 @@
       <c r="M262" s="16"/>
       <c r="N262" s="17"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -7617,7 +7674,7 @@
       <c r="M263" s="16"/>
       <c r="N263" s="17"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -7639,7 +7696,7 @@
       <c r="M264" s="16"/>
       <c r="N264" s="17"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -7661,7 +7718,7 @@
       <c r="M265" s="16"/>
       <c r="N265" s="17"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -7683,7 +7740,7 @@
       <c r="M266" s="16"/>
       <c r="N266" s="17"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -7705,7 +7762,7 @@
       <c r="M267" s="16"/>
       <c r="N267" s="17"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -7727,7 +7784,7 @@
       <c r="M268" s="16"/>
       <c r="N268" s="17"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -7749,7 +7806,7 @@
       <c r="M269" s="16"/>
       <c r="N269" s="17"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -7771,7 +7828,7 @@
       <c r="M270" s="16"/>
       <c r="N270" s="17"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -7793,7 +7850,7 @@
       <c r="M271" s="16"/>
       <c r="N271" s="17"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -7815,7 +7872,7 @@
       <c r="M272" s="16"/>
       <c r="N272" s="17"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -7837,7 +7894,7 @@
       <c r="M273" s="16"/>
       <c r="N273" s="17"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -7859,7 +7916,7 @@
       <c r="M274" s="16"/>
       <c r="N274" s="17"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -7881,7 +7938,7 @@
       <c r="M275" s="16"/>
       <c r="N275" s="17"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -7903,7 +7960,7 @@
       <c r="M276" s="16"/>
       <c r="N276" s="17"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -7925,7 +7982,7 @@
       <c r="M277" s="16"/>
       <c r="N277" s="17"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -7947,7 +8004,7 @@
       <c r="M278" s="16"/>
       <c r="N278" s="17"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -7969,7 +8026,7 @@
       <c r="M279" s="16"/>
       <c r="N279" s="17"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -7991,7 +8048,7 @@
       <c r="M280" s="16"/>
       <c r="N280" s="17"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -8013,7 +8070,7 @@
       <c r="M281" s="16"/>
       <c r="N281" s="17"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -8035,7 +8092,7 @@
       <c r="M282" s="16"/>
       <c r="N282" s="17"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -8057,7 +8114,7 @@
       <c r="M283" s="16"/>
       <c r="N283" s="17"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -8079,7 +8136,7 @@
       <c r="M284" s="16"/>
       <c r="N284" s="17"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -8101,7 +8158,7 @@
       <c r="M285" s="16"/>
       <c r="N285" s="17"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -8123,7 +8180,7 @@
       <c r="M286" s="16"/>
       <c r="N286" s="17"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -8145,7 +8202,7 @@
       <c r="M287" s="16"/>
       <c r="N287" s="17"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -8167,7 +8224,7 @@
       <c r="M288" s="16"/>
       <c r="N288" s="17"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -8189,7 +8246,7 @@
       <c r="M289" s="16"/>
       <c r="N289" s="17"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -8211,7 +8268,7 @@
       <c r="M290" s="16"/>
       <c r="N290" s="17"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -8233,7 +8290,7 @@
       <c r="M291" s="16"/>
       <c r="N291" s="17"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -8255,7 +8312,7 @@
       <c r="M292" s="16"/>
       <c r="N292" s="17"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -8277,7 +8334,7 @@
       <c r="M293" s="16"/>
       <c r="N293" s="17"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -8299,7 +8356,7 @@
       <c r="M294" s="16"/>
       <c r="N294" s="17"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -8321,7 +8378,7 @@
       <c r="M295" s="16"/>
       <c r="N295" s="17"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -8343,7 +8400,7 @@
       <c r="M296" s="16"/>
       <c r="N296" s="17"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -8365,7 +8422,7 @@
       <c r="M297" s="16"/>
       <c r="N297" s="17"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -8387,7 +8444,7 @@
       <c r="M298" s="16"/>
       <c r="N298" s="17"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -8409,7 +8466,7 @@
       <c r="M299" s="16"/>
       <c r="N299" s="17"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -8431,7 +8488,7 @@
       <c r="M300" s="16"/>
       <c r="N300" s="17"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -8453,7 +8510,7 @@
       <c r="M301" s="16"/>
       <c r="N301" s="17"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -8475,7 +8532,7 @@
       <c r="M302" s="16"/>
       <c r="N302" s="17"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -8497,7 +8554,7 @@
       <c r="M303" s="16"/>
       <c r="N303" s="17"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -8519,7 +8576,7 @@
       <c r="M304" s="16"/>
       <c r="N304" s="17"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -8541,7 +8598,7 @@
       <c r="M305" s="16"/>
       <c r="N305" s="17"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -8563,7 +8620,7 @@
       <c r="M306" s="16"/>
       <c r="N306" s="17"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -8585,7 +8642,7 @@
       <c r="M307" s="16"/>
       <c r="N307" s="17"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -8607,7 +8664,7 @@
       <c r="M308" s="16"/>
       <c r="N308" s="17"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -8629,7 +8686,7 @@
       <c r="M309" s="16"/>
       <c r="N309" s="17"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -8651,7 +8708,7 @@
       <c r="M310" s="16"/>
       <c r="N310" s="17"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -8673,7 +8730,7 @@
       <c r="M311" s="16"/>
       <c r="N311" s="17"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -8695,7 +8752,7 @@
       <c r="M312" s="16"/>
       <c r="N312" s="17"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -8717,7 +8774,7 @@
       <c r="M313" s="16"/>
       <c r="N313" s="17"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -8739,7 +8796,7 @@
       <c r="M314" s="16"/>
       <c r="N314" s="17"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -8761,7 +8818,7 @@
       <c r="M315" s="16"/>
       <c r="N315" s="17"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -8783,7 +8840,7 @@
       <c r="M316" s="16"/>
       <c r="N316" s="17"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -8805,7 +8862,7 @@
       <c r="M317" s="16"/>
       <c r="N317" s="17"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -8827,7 +8884,7 @@
       <c r="M318" s="16"/>
       <c r="N318" s="17"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -8849,7 +8906,7 @@
       <c r="M319" s="16"/>
       <c r="N319" s="17"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -8871,7 +8928,7 @@
       <c r="M320" s="16"/>
       <c r="N320" s="17"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -8893,7 +8950,7 @@
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -8915,7 +8972,7 @@
       <c r="M322" s="16"/>
       <c r="N322" s="17"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -8937,7 +8994,7 @@
       <c r="M323" s="16"/>
       <c r="N323" s="17"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -8959,7 +9016,7 @@
       <c r="M324" s="16"/>
       <c r="N324" s="17"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -8981,7 +9038,7 @@
       <c r="M325" s="16"/>
       <c r="N325" s="17"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -9003,7 +9060,7 @@
       <c r="M326" s="16"/>
       <c r="N326" s="17"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -9025,7 +9082,7 @@
       <c r="M327" s="16"/>
       <c r="N327" s="17"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -9047,7 +9104,7 @@
       <c r="M328" s="16"/>
       <c r="N328" s="17"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -9069,7 +9126,7 @@
       <c r="M329" s="16"/>
       <c r="N329" s="17"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -9091,7 +9148,7 @@
       <c r="M330" s="16"/>
       <c r="N330" s="17"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -9113,7 +9170,7 @@
       <c r="M331" s="16"/>
       <c r="N331" s="17"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -9135,7 +9192,7 @@
       <c r="M332" s="16"/>
       <c r="N332" s="17"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -9157,7 +9214,7 @@
       <c r="M333" s="16"/>
       <c r="N333" s="17"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -9179,7 +9236,7 @@
       <c r="M334" s="16"/>
       <c r="N334" s="17"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -9201,7 +9258,7 @@
       <c r="M335" s="16"/>
       <c r="N335" s="17"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -9223,7 +9280,7 @@
       <c r="M336" s="16"/>
       <c r="N336" s="17"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -9245,7 +9302,7 @@
       <c r="M337" s="16"/>
       <c r="N337" s="17"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -9267,7 +9324,7 @@
       <c r="M338" s="16"/>
       <c r="N338" s="17"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -9289,7 +9346,7 @@
       <c r="M339" s="16"/>
       <c r="N339" s="17"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -9311,7 +9368,7 @@
       <c r="M340" s="16"/>
       <c r="N340" s="17"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -9333,7 +9390,7 @@
       <c r="M341" s="16"/>
       <c r="N341" s="17"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -9355,7 +9412,7 @@
       <c r="M342" s="16"/>
       <c r="N342" s="17"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -9377,7 +9434,7 @@
       <c r="M343" s="16"/>
       <c r="N343" s="17"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -9399,7 +9456,7 @@
       <c r="M344" s="16"/>
       <c r="N344" s="17"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -9421,7 +9478,7 @@
       <c r="M345" s="16"/>
       <c r="N345" s="17"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -9443,7 +9500,7 @@
       <c r="M346" s="16"/>
       <c r="N346" s="17"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -9465,7 +9522,7 @@
       <c r="M347" s="16"/>
       <c r="N347" s="17"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -9487,7 +9544,7 @@
       <c r="M348" s="16"/>
       <c r="N348" s="17"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -9509,7 +9566,7 @@
       <c r="M349" s="16"/>
       <c r="N349" s="17"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -9531,7 +9588,7 @@
       <c r="M350" s="16"/>
       <c r="N350" s="17"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -9553,7 +9610,7 @@
       <c r="M351" s="16"/>
       <c r="N351" s="17"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -9575,7 +9632,7 @@
       <c r="M352" s="16"/>
       <c r="N352" s="17"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -9597,7 +9654,7 @@
       <c r="M353" s="16"/>
       <c r="N353" s="17"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -9619,7 +9676,7 @@
       <c r="M354" s="16"/>
       <c r="N354" s="17"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -9641,7 +9698,7 @@
       <c r="M355" s="16"/>
       <c r="N355" s="17"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -9663,7 +9720,7 @@
       <c r="M356" s="16"/>
       <c r="N356" s="17"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -9685,7 +9742,7 @@
       <c r="M357" s="16"/>
       <c r="N357" s="17"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -9707,7 +9764,7 @@
       <c r="M358" s="16"/>
       <c r="N358" s="17"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -9729,7 +9786,7 @@
       <c r="M359" s="16"/>
       <c r="N359" s="17"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -9751,7 +9808,7 @@
       <c r="M360" s="16"/>
       <c r="N360" s="17"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -9773,7 +9830,7 @@
       <c r="M361" s="16"/>
       <c r="N361" s="17"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -9795,7 +9852,7 @@
       <c r="M362" s="16"/>
       <c r="N362" s="17"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -9817,7 +9874,7 @@
       <c r="M363" s="16"/>
       <c r="N363" s="17"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -9839,7 +9896,7 @@
       <c r="M364" s="16"/>
       <c r="N364" s="17"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -9861,7 +9918,7 @@
       <c r="M365" s="16"/>
       <c r="N365" s="17"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -9883,7 +9940,7 @@
       <c r="M366" s="16"/>
       <c r="N366" s="17"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -9905,7 +9962,7 @@
       <c r="M367" s="16"/>
       <c r="N367" s="17"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -9927,7 +9984,7 @@
       <c r="M368" s="16"/>
       <c r="N368" s="17"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -9949,7 +10006,7 @@
       <c r="M369" s="16"/>
       <c r="N369" s="17"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -9971,7 +10028,7 @@
       <c r="M370" s="16"/>
       <c r="N370" s="17"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -9993,7 +10050,7 @@
       <c r="M371" s="16"/>
       <c r="N371" s="17"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -10015,7 +10072,7 @@
       <c r="M372" s="16"/>
       <c r="N372" s="17"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -10037,7 +10094,7 @@
       <c r="M373" s="16"/>
       <c r="N373" s="17"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -10059,7 +10116,7 @@
       <c r="M374" s="16"/>
       <c r="N374" s="17"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -10081,7 +10138,7 @@
       <c r="M375" s="16"/>
       <c r="N375" s="17"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -10103,7 +10160,7 @@
       <c r="M376" s="16"/>
       <c r="N376" s="17"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -10125,7 +10182,7 @@
       <c r="M377" s="16"/>
       <c r="N377" s="17"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -10147,7 +10204,7 @@
       <c r="M378" s="16"/>
       <c r="N378" s="17"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -10169,7 +10226,7 @@
       <c r="M379" s="16"/>
       <c r="N379" s="17"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -10191,7 +10248,7 @@
       <c r="M380" s="16"/>
       <c r="N380" s="17"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -10213,7 +10270,7 @@
       <c r="M381" s="16"/>
       <c r="N381" s="17"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -10235,7 +10292,7 @@
       <c r="M382" s="16"/>
       <c r="N382" s="17"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -10257,7 +10314,7 @@
       <c r="M383" s="16"/>
       <c r="N383" s="17"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -10279,7 +10336,7 @@
       <c r="M384" s="16"/>
       <c r="N384" s="17"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -10301,7 +10358,7 @@
       <c r="M385" s="16"/>
       <c r="N385" s="17"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -10323,7 +10380,7 @@
       <c r="M386" s="16"/>
       <c r="N386" s="17"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -10345,7 +10402,7 @@
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -10367,7 +10424,7 @@
       <c r="M388" s="16"/>
       <c r="N388" s="17"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -10389,7 +10446,7 @@
       <c r="M389" s="16"/>
       <c r="N389" s="17"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -10411,7 +10468,7 @@
       <c r="M390" s="16"/>
       <c r="N390" s="17"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -10433,7 +10490,7 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -10455,7 +10512,7 @@
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -10477,7 +10534,7 @@
       <c r="M393" s="16"/>
       <c r="N393" s="17"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -10499,7 +10556,7 @@
       <c r="M394" s="16"/>
       <c r="N394" s="17"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -10521,7 +10578,7 @@
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -10543,7 +10600,7 @@
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -10565,7 +10622,7 @@
       <c r="M397" s="16"/>
       <c r="N397" s="17"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -10587,7 +10644,7 @@
       <c r="M398" s="16"/>
       <c r="N398" s="17"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -10609,7 +10666,7 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -10631,7 +10688,7 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D41B41064DFFF035/Desktop/pythonass/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE8B3A85-38F4-4DDE-B908-C6E276138B1A}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A2EBA22-F370-4128-A1E3-D0023BCC3F65}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>fever</t>
+  </si>
+  <si>
+    <t>o</t>
   </si>
 </sst>
 </file>
@@ -2962,184 +2965,352 @@
       <c r="A50" s="13">
         <v>46298</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="B50" s="14">
+        <v>700</v>
+      </c>
+      <c r="C50" s="14">
+        <v>100</v>
+      </c>
+      <c r="D50" s="14">
+        <v>50</v>
+      </c>
+      <c r="E50" s="14">
+        <v>80</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H50" s="14">
+        <v>460</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="13">
         <v>46299</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="B51" s="14">
+        <v>650</v>
+      </c>
+      <c r="C51" s="14">
+        <v>120</v>
+      </c>
+      <c r="D51" s="14">
+        <v>40</v>
+      </c>
+      <c r="E51" s="14">
+        <v>50</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>370</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>210</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="13">
         <v>46300</v>
       </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="B52" s="14">
+        <v>600</v>
+      </c>
+      <c r="C52" s="14">
+        <v>100</v>
+      </c>
+      <c r="D52" s="14">
+        <v>30</v>
+      </c>
+      <c r="E52" s="14">
+        <v>30</v>
+      </c>
+      <c r="F52" s="14">
+        <v>240</v>
+      </c>
+      <c r="G52" s="14">
+        <v>4</v>
+      </c>
+      <c r="H52" s="14">
+        <v>200</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+        <v>240</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="13">
         <v>46301</v>
       </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="B53" s="14">
+        <v>600</v>
+      </c>
+      <c r="C53" s="14">
+        <v>50</v>
+      </c>
+      <c r="D53" s="14">
+        <v>40</v>
+      </c>
+      <c r="E53" s="14">
+        <v>40</v>
+      </c>
+      <c r="F53" s="14">
+        <v>420</v>
+      </c>
+      <c r="G53" s="14">
+        <v>7</v>
+      </c>
+      <c r="H53" s="14">
+        <v>100</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B54" s="14">
+        <v>650</v>
+      </c>
+      <c r="C54" s="14">
+        <v>60</v>
+      </c>
+      <c r="D54" s="14">
+        <v>30</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>420</v>
+      </c>
+      <c r="G54" s="14">
+        <v>7</v>
+      </c>
+      <c r="H54" s="14">
+        <v>60</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B55" s="14">
+        <v>600</v>
+      </c>
+      <c r="C55" s="14">
+        <v>60</v>
+      </c>
+      <c r="D55" s="14">
+        <v>50</v>
+      </c>
+      <c r="E55" s="14">
+        <v>35</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>100</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
+        <v>595</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B56" s="14">
+        <v>550</v>
+      </c>
+      <c r="C56" s="14">
+        <v>90</v>
+      </c>
+      <c r="D56" s="14">
+        <v>100</v>
+      </c>
+      <c r="E56" s="14">
+        <v>40</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>100</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
+        <v>560</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B57" s="14">
+        <v>600</v>
+      </c>
+      <c r="C57" s="14">
+        <v>60</v>
+      </c>
+      <c r="D57" s="14">
+        <v>100</v>
+      </c>
+      <c r="E57" s="14">
+        <v>50</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>100</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
+        <v>530</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D41B41064DFFF035/Desktop/pythonass/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Desktop\pythonass\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="8_{ACC851C4-A9E2-44FB-A0C0-4C5573B75CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A2EBA22-F370-4128-A1E3-D0023BCC3F65}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D7BDBB-B082-4134-A858-2BEA8DF3CC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>o</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -3314,25 +3317,47 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B58" s="14">
+        <v>550</v>
+      </c>
+      <c r="C58" s="14">
+        <v>60</v>
+      </c>
+      <c r="D58" s="14">
+        <v>120</v>
+      </c>
+      <c r="E58" s="14">
+        <v>60</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>100</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Desktop\pythonass\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D7BDBB-B082-4134-A858-2BEA8DF3CC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB108A59-EEA0-47DE-BAD3-1F081035979F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3361,47 +3361,91 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B59" s="14">
+        <v>400</v>
+      </c>
+      <c r="C59" s="14">
+        <v>0</v>
+      </c>
+      <c r="D59" s="14">
+        <v>500</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>100</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B60" s="14">
+        <v>500</v>
+      </c>
+      <c r="C60" s="14">
+        <v>30</v>
+      </c>
+      <c r="D60" s="14">
+        <v>550</v>
+      </c>
+      <c r="E60" s="14">
+        <v>30</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>50</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Desktop\pythonass\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB108A59-EEA0-47DE-BAD3-1F081035979F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9A6811-05DE-4518-90D0-F2121710E43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3449,69 +3449,135 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B61" s="14">
+        <v>550</v>
+      </c>
+      <c r="C61" s="14">
+        <v>30</v>
+      </c>
+      <c r="D61" s="14">
+        <v>600</v>
+      </c>
+      <c r="E61" s="14">
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>100</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
+        <v>160</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B62" s="14">
+        <v>450</v>
+      </c>
+      <c r="C62" s="14">
+        <v>0</v>
+      </c>
+      <c r="D62" s="14">
+        <v>550</v>
+      </c>
+      <c r="E62" s="14">
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>60</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B63" s="14">
+        <v>500</v>
+      </c>
+      <c r="C63" s="14">
+        <v>0</v>
+      </c>
+      <c r="D63" s="14">
+        <v>500</v>
+      </c>
+      <c r="E63" s="14">
+        <v>60</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>50</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
+        <v>330</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Desktop\pythonass\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9A6811-05DE-4518-90D0-F2121710E43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CA5363-65B9-4351-B523-03007A94B253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3581,51 +3581,97 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B64" s="14">
+        <v>450</v>
+      </c>
+      <c r="C64" s="14">
+        <v>0</v>
+      </c>
+      <c r="D64" s="14">
+        <v>550</v>
+      </c>
+      <c r="E64" s="14">
+        <v>30</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>100</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
+        <v>310</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B65" s="14">
+        <v>500</v>
+      </c>
+      <c r="C65" s="14">
+        <v>0</v>
+      </c>
+      <c r="D65" s="14">
+        <v>600</v>
+      </c>
+      <c r="E65" s="14">
+        <v>30</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>100</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
+        <v>210</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
+      <c r="A66" s="13">
+        <v>46314</v>
+      </c>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Desktop\pythonass\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CA5363-65B9-4351-B523-03007A94B253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9826518B-626E-4BB2-B35F-A10E76874558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1214,7 +1214,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G10" s="14">
         <v>4</v>
@@ -1223,12 +1223,12 @@
         <v>150</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" ref="I10:I69" si="0">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
-        <v>1110</v>
+        <f t="shared" ref="I10:I68" si="0">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
+        <v>1070</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" ref="J10:J69" si="1">IF(I10="","",1440-I10)</f>
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>60</v>
@@ -1258,7 +1258,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="14">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G11" s="14">
         <v>7</v>
@@ -1268,11 +1268,11 @@
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1320</v>
+        <v>1310</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>60</v>
@@ -1302,7 +1302,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="14">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G12" s="14">
         <v>7</v>
@@ -1312,11 +1312,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>60</v>
@@ -1346,7 +1346,7 @@
         <v>40</v>
       </c>
       <c r="F13" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G13" s="14">
         <v>4</v>
@@ -1356,11 +1356,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>1080</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1390,7 +1390,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G14" s="14">
         <v>4</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>970</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>49</v>
@@ -1522,7 +1522,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G17" s="14">
         <v>4</v>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1070</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
@@ -1566,7 +1566,7 @@
         <v>10</v>
       </c>
       <c r="F18" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
@@ -1576,11 +1576,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>970</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>470</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>49</v>
@@ -1654,7 +1654,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G20" s="14">
         <v>4</v>
@@ -1664,11 +1664,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>60</v>
@@ -1698,7 +1698,7 @@
         <v>120</v>
       </c>
       <c r="F21" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G21" s="14">
         <v>5</v>
@@ -1708,11 +1708,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>62</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G24" s="14">
         <v>5</v>
@@ -1840,11 +1840,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>60</v>
@@ -1874,7 +1874,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G25" s="14">
         <v>7</v>
@@ -1884,11 +1884,11 @@
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>1310</v>
+        <v>1240</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>62</v>
@@ -1918,7 +1918,7 @@
         <v>130</v>
       </c>
       <c r="F26" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G26" s="14">
         <v>7</v>
@@ -1928,11 +1928,11 @@
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>1310</v>
+        <v>1240</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
@@ -1972,11 +1972,11 @@
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>690</v>
+        <v>740</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>64</v>
@@ -2190,7 +2190,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G32" s="14">
         <v>7</v>
@@ -2200,11 +2200,11 @@
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>1310</v>
+        <v>1240</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>49</v>
@@ -2234,7 +2234,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G33" s="14">
         <v>7</v>
@@ -2244,11 +2244,11 @@
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>1350</v>
+        <v>1280</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>64</v>
@@ -2278,7 +2278,7 @@
         <v>40</v>
       </c>
       <c r="F34" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G34" s="14">
         <v>4</v>
@@ -2288,11 +2288,11 @@
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1160</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>62</v>
@@ -2322,7 +2322,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G35" s="14">
         <v>5</v>
@@ -2332,11 +2332,11 @@
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1420</v>
+        <v>1370</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>49</v>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G38" s="14">
         <v>4</v>
@@ -2463,11 +2463,11 @@
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>942</v>
+        <v>902</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>498</v>
+        <v>538</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>49</v>
@@ -2497,7 +2497,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G39" s="14">
         <v>7</v>
@@ -2507,11 +2507,11 @@
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>1270</v>
+        <v>1200</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>60</v>
@@ -2541,7 +2541,7 @@
         <v>30</v>
       </c>
       <c r="F40" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G40" s="14">
         <v>7</v>
@@ -2551,11 +2551,11 @@
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>1196</v>
+        <v>1126</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>60</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G41" s="14">
         <v>4</v>
@@ -2595,11 +2595,11 @@
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1160</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>62</v>
@@ -2629,7 +2629,7 @@
         <v>40</v>
       </c>
       <c r="F42" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G42" s="14">
         <v>5</v>
@@ -2639,11 +2639,11 @@
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>1240</v>
+        <v>1190</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>49</v>
@@ -3069,7 +3069,7 @@
         <v>30</v>
       </c>
       <c r="F52" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G52" s="14">
         <v>4</v>
@@ -3079,11 +3079,11 @@
       </c>
       <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1160</v>
       </c>
       <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="K52" s="16" t="s">
         <v>49</v>
@@ -3113,7 +3113,7 @@
         <v>40</v>
       </c>
       <c r="F53" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G53" s="14">
         <v>7</v>
@@ -3123,11 +3123,11 @@
       </c>
       <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v>1250</v>
+        <v>1180</v>
       </c>
       <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="K53" s="16" t="s">
         <v>60</v>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G54" s="14">
         <v>7</v>
@@ -3167,11 +3167,11 @@
       </c>
       <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1150</v>
       </c>
       <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="K54" s="16" t="s">
         <v>60</v>
@@ -3672,90 +3672,176 @@
       <c r="A66" s="13">
         <v>46314</v>
       </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="B66" s="14">
+        <v>600</v>
+      </c>
+      <c r="C66" s="14">
+        <v>30</v>
+      </c>
+      <c r="D66" s="14">
+        <v>120</v>
+      </c>
+      <c r="E66" s="14">
+        <v>60</v>
+      </c>
+      <c r="F66" s="14">
+        <v>200</v>
+      </c>
+      <c r="G66" s="14">
+        <v>4</v>
+      </c>
+      <c r="H66" s="14">
+        <v>50</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B67" s="14">
+        <v>500</v>
+      </c>
+      <c r="C67" s="14">
+        <v>0</v>
+      </c>
+      <c r="D67" s="14">
+        <v>60</v>
+      </c>
+      <c r="E67" s="14">
+        <v>120</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>100</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B68" s="14">
+        <v>550</v>
+      </c>
+      <c r="C68" s="14">
+        <v>0</v>
+      </c>
+      <c r="D68" s="14">
+        <v>60</v>
+      </c>
+      <c r="E68" s="14">
+        <v>150</v>
+      </c>
+      <c r="F68" s="14">
+        <v>350</v>
+      </c>
+      <c r="G68" s="14">
+        <v>7</v>
+      </c>
+      <c r="H68" s="14">
+        <v>100</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
+        <v>230</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B69" s="14">
+        <v>600</v>
+      </c>
+      <c r="C69" s="14">
+        <v>0</v>
+      </c>
+      <c r="D69" s="14">
+        <v>60</v>
+      </c>
+      <c r="E69" s="14">
+        <v>100</v>
+      </c>
+      <c r="F69" s="14">
+        <v>200</v>
+      </c>
+      <c r="G69" s="14">
+        <v>4</v>
+      </c>
+      <c r="H69" s="14">
+        <v>400</v>
+      </c>
+      <c r="I69" s="15">
+        <f>IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
+        <v>1360</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Desktop\pythonass\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9826518B-626E-4BB2-B35F-A10E76874558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A8E42D-EFB9-4D64-AFCC-0E891D2D33F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3845,179 +3845,355 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B70" s="14">
+        <v>550</v>
+      </c>
+      <c r="C70" s="14">
+        <v>0</v>
+      </c>
+      <c r="D70" s="14">
+        <v>120</v>
+      </c>
+      <c r="E70" s="14">
+        <v>50</v>
+      </c>
+      <c r="F70" s="14">
+        <v>250</v>
+      </c>
+      <c r="G70" s="14">
+        <v>5</v>
+      </c>
+      <c r="H70" s="14">
+        <v>0</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B71" s="14">
+        <v>600</v>
+      </c>
+      <c r="C71" s="14">
+        <v>50</v>
+      </c>
+      <c r="D71" s="14">
+        <v>200</v>
+      </c>
+      <c r="E71" s="14">
+        <v>60</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>100</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B72" s="14">
+        <v>600</v>
+      </c>
+      <c r="C72" s="14">
+        <v>50</v>
+      </c>
+      <c r="D72" s="14">
+        <v>200</v>
+      </c>
+      <c r="E72" s="14">
+        <v>60</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>100</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B73" s="14">
+        <v>700</v>
+      </c>
+      <c r="C73" s="14">
+        <v>50</v>
+      </c>
+      <c r="D73" s="14">
+        <v>250</v>
+      </c>
+      <c r="E73" s="14">
+        <v>120</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>100</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B74" s="14">
+        <v>600</v>
+      </c>
+      <c r="C74" s="14">
+        <v>0</v>
+      </c>
+      <c r="D74" s="14">
+        <v>200</v>
+      </c>
+      <c r="E74" s="14">
+        <v>150</v>
+      </c>
+      <c r="F74" s="14">
+        <v>250</v>
+      </c>
+      <c r="G74" s="14">
+        <v>5</v>
+      </c>
+      <c r="H74" s="14">
+        <v>50</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B75" s="14">
+        <v>700</v>
+      </c>
+      <c r="C75" s="14">
+        <v>0</v>
+      </c>
+      <c r="D75" s="14">
+        <v>120</v>
+      </c>
+      <c r="E75" s="14">
+        <v>100</v>
+      </c>
+      <c r="F75" s="14">
+        <v>300</v>
+      </c>
+      <c r="G75" s="14">
+        <v>6</v>
+      </c>
+      <c r="H75" s="14">
+        <v>0</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B76" s="14">
+        <v>650</v>
+      </c>
+      <c r="C76" s="14">
+        <v>50</v>
+      </c>
+      <c r="D76" s="14">
+        <v>200</v>
+      </c>
+      <c r="E76" s="14">
+        <v>300</v>
+      </c>
+      <c r="F76" s="14">
+        <v>200</v>
+      </c>
+      <c r="G76" s="14">
+        <v>4</v>
+      </c>
+      <c r="H76" s="14">
+        <v>0</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B77" s="14">
+        <v>750</v>
+      </c>
+      <c r="C77" s="14">
+        <v>50</v>
+      </c>
+      <c r="D77" s="14">
+        <v>100</v>
+      </c>
+      <c r="E77" s="14">
+        <v>0</v>
+      </c>
+      <c r="F77" s="14">
+        <v>250</v>
+      </c>
+      <c r="G77" s="14">
+        <v>5</v>
+      </c>
+      <c r="H77" s="14">
+        <v>100</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">

--- a/12622743.xlsx
+++ b/12622743.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Desktop\pythonass\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A8E42D-EFB9-4D64-AFCC-0E891D2D33F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8871C2C-2BD3-41EE-ACE0-E79E0C7BACC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4197,25 +4197,47 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13">
+        <v>46326</v>
+      </c>
+      <c r="B78" s="14">
+        <v>650</v>
+      </c>
+      <c r="C78" s="14">
+        <v>0</v>
+      </c>
+      <c r="D78" s="14">
+        <v>250</v>
+      </c>
+      <c r="E78" s="14">
+        <v>200</v>
+      </c>
+      <c r="F78" s="14">
+        <v>0</v>
+      </c>
+      <c r="G78" s="14">
+        <v>0</v>
+      </c>
+      <c r="H78" s="14">
+        <v>50</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
+        <v>290</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
